--- a/monitoring_weighted_similarity.xlsx
+++ b/monitoring_weighted_similarity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,47 +3298,45 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GAMMA RAYA, CV</t>
+          <t>SEXY ROAD INDO, CV</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jalan Rusli Datau 1 Perumahan Alya III Blok B Nomor 2</t>
+          <t>Perum Asabri Blok E/03</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GAMMA RAYA, CV</t>
+          <t>MARKA INDAH, CV</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="J54" t="n">
         <v>100</v>
       </c>
-      <c r="K54" t="n">
-        <v>92.92929292929293</v>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>94.72186655285246</v>
+        <v>67.76859504132231</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3353,45 +3351,47 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TRI BAROKAH PERKASA, PT</t>
+          <t>GAMMA RAYA, CV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jl. Kasmat Lahay</t>
+          <t>Jalan Rusli Datau 1 Perumahan Alya III Blok B Nomor 2</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1191</v>
+        <v>153</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PUTRA MITRA PERKASA, CV</t>
+          <t>GAMMA RAYA, CV</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>65.21739130434783</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
         <v>100</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>92.92929292929293</v>
+      </c>
       <c r="L55" t="n">
-        <v>70.37037037037037</v>
+        <v>94.72186655285246</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -3406,41 +3406,41 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INDO KONSTRUKSI PERSADA, PT</t>
+          <t>TRI BAROKAH PERKASA, PT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jalan Sun Ismail Perum Latoro</t>
+          <t>Jl. Kasmat Lahay</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>207</v>
+        <v>1191</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LUTSIR PERSADA JAYA, PT</t>
+          <t>PUTRA MITRA PERKASA, CV</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>60</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="J56" t="n">
         <v>100</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>65.16129032258064</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3459,41 +3459,41 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HAVANA TUNAS GEMILANG, PT</t>
+          <t>INDO KONSTRUKSI PERSADA, PT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JALAN DIPENOGORO BLOK PLAN PERKANTORAN MARISA</t>
+          <t>Jalan Sun Ismail Perum Latoro</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1481</v>
+        <v>207</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>LUTSIR PERSADA JAYA, PT</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>56.00000000000001</v>
+        <v>60</v>
       </c>
       <c r="J57" t="n">
         <v>100</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>62.06896551724139</v>
+        <v>65.16129032258064</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEGA UTAMA MARISA, CV</t>
+          <t>HAVANA TUNAS GEMILANG, PT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3522,15 +3522,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DUSUN BATU PASANG</t>
+          <t>JALAN DIPENOGORO BLOK PLAN PERKANTORAN MARISA</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1426</v>
+        <v>1481</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MULIA MULTI MANDIRI, CV</t>
+          <t>RISKY MAHARANI ENERGI, PT</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3539,14 +3539,14 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>63.63636363636363</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="J58" t="n">
         <v>100</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>69.45454545454545</v>
+        <v>62.06896551724139</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3565,43 +3565,41 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ANNISA RAMADHANI PROPERTINDO, PT</t>
+          <t>MEGA UTAMA MARISA, CV</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jalan Profesor H.B Jassin Nomor 303</t>
+          <t>DUSUN BATU PASANG</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2035</v>
+        <v>1426</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>POPA EYATO JAYA TAMA, PT</t>
+          <t>MULIA MULTI MANDIRI, CV</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>46.42857142857143</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="J59" t="n">
         <v>100</v>
       </c>
-      <c r="K59" t="n">
-        <v>56.14035087719298</v>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>54.23417699177521</v>
+        <v>69.45454545454545</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3620,7 +3618,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NJ GROUP, CV</t>
+          <t>ANNISA RAMADHANI PROPERTINDO, PT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3630,15 +3628,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Perumahan Awara Karya Blok A.08</t>
+          <t>Jalan Profesor H.B Jassin Nomor 303</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1790</v>
+        <v>2035</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>RIZKIA LESTARI, CV</t>
+          <t>POPA EYATO JAYA TAMA, PT</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3647,16 +3645,16 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>40</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="J60" t="n">
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>75.86206896551724</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="L60" t="n">
-        <v>68.76008804108584</v>
+        <v>54.23417699177521</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3675,41 +3673,43 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SULTAN JAYA NUSANTARA, CV</t>
+          <t>NJ GROUP, CV</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kelurahan Kayumerah</t>
+          <t>Perumahan Awara Karya Blok A.08</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>296</v>
+        <v>1790</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>KARYA PATRIOT NUSANTARA, CV</t>
+          <t>RIZKIA LESTARI, CV</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>73.07692307692308</v>
+        <v>40</v>
       </c>
       <c r="J61" t="n">
         <v>100</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>75.86206896551724</v>
+      </c>
       <c r="L61" t="n">
-        <v>76.79045092838197</v>
+        <v>68.76008804108584</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>INDRA PRAHASTA, CV</t>
+          <t>SULTAN JAYA NUSANTARA, CV</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3738,15 +3738,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Telaga Biru</t>
+          <t>Kelurahan Kayumerah</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>INKA PRATAMA, CV</t>
+          <t>KARYA PATRIOT NUSANTARA, CV</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3755,14 +3755,14 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>76.47058823529412</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="J62" t="n">
         <v>100</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>80.74866310160428</v>
+        <v>76.79045092838197</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3781,41 +3781,41 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MOTIKACI FAMILY GROUP, CV</t>
+          <t>INDRA PRAHASTA, CV</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dusun Pasar Lama, Desa Moluo, Kecamatan Kwandang, Kabupaten Gorontalo Utara.</t>
+          <t>Telaga Biru</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1597</v>
+        <v>292</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>TIRTA TARUNA, CV</t>
+          <t>INKA PRATAMA, CV</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>53.65853658536586</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="J63" t="n">
         <v>100</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>60.05046257359125</v>
+        <v>80.74866310160428</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3834,41 +3834,41 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAHARANI PERSADA KONSTRUKSI, PT</t>
+          <t>MOTIKACI FAMILY GROUP, CV</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JALAN PROF. DR. ALOE SABOE</t>
+          <t>Dusun Pasar Lama, Desa Moluo, Kecamatan Kwandang, Kabupaten Gorontalo Utara.</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1481</v>
+        <v>1597</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>TIRTA TARUNA, CV</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>60.71428571428572</v>
+        <v>53.65853658536586</v>
       </c>
       <c r="J64" t="n">
         <v>100</v>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>65.20408163265307</v>
+        <v>60.05046257359125</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3887,47 +3887,45 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>MAHARANI PERSADA KONSTRUKSI, PT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jalan Kancil</t>
+          <t>JALAN PROF. DR. ALOE SABOE</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>158</v>
+        <v>1481</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>RISKY MAHARANI ENERGI, PT</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>100</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="J65" t="n">
         <v>100</v>
       </c>
-      <c r="K65" t="n">
-        <v>85.71428571428572</v>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>94.47004608294931</v>
+        <v>65.20408163265307</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3942,30 +3940,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
+          <t>RARA BERKAH, CV</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jalan husin DJ Rahman</t>
+          <t>Jalan Kancil</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
+          <t>RARA BERKAH, CV</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3975,10 +3973,10 @@
         <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>92.30769230769231</v>
+        <v>85.71428571428572</v>
       </c>
       <c r="L66" t="n">
-        <v>95.63409563409563</v>
+        <v>94.47004608294931</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -3997,47 +3995,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SANUR ARA, CV</t>
+          <t>ALL AHAD, CV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jalan Gelatik No. 26</t>
+          <t>Jalan husin DJ Rahman</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SETIA KARYA SEJATI, CV</t>
+          <t>ALL AHAD, CV</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
         <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>78.94736842105263</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="L67" t="n">
-        <v>67.53911806543385</v>
+        <v>95.63409563409563</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4052,41 +4050,43 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PUTRA ECHAXEL, CV</t>
+          <t>SANUR ARA, CV</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jalan Sultan Botutihe</t>
+          <t>Jalan Gelatik No. 26</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1264</v>
+        <v>146</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EKA PUTRA, CV</t>
+          <t>SETIA KARYA SEJATI, CV</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>73.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="J68" t="n">
         <v>100</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>78.94736842105263</v>
+      </c>
       <c r="L68" t="n">
-        <v>78.41269841269842</v>
+        <v>67.53911806543385</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4105,43 +4105,41 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VIJAYA KARYA UTAMA, PT</t>
+          <t>PUTRA ECHAXEL, CV</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jl. Rusli Datau 2 No 4</t>
+          <t>Jalan Sultan Botutihe</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2215</v>
+        <v>1264</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MITRA JAYA MULTI SARANA, CV</t>
+          <t>EKA PUTRA, CV</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>44.89795918367348</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="J69" t="n">
         <v>100</v>
       </c>
-      <c r="K69" t="n">
-        <v>92.6829268292683</v>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>71.3912394225983</v>
+        <v>78.41269841269842</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4160,41 +4158,43 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AQIFFA JAYA MANDIRI, CV</t>
+          <t>VIJAYA KARYA UTAMA, PT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dusun Lamahu Desa Sipatana</t>
+          <t>Jl. Rusli Datau 2 No 4</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1347</v>
+        <v>2215</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JAYA MANDIRI PERSADA, CV</t>
+          <t>MITRA JAYA MULTI SARANA, CV</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>68.08510638297872</v>
+        <v>44.89795918367348</v>
       </c>
       <c r="J70" t="n">
         <v>100</v>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>92.6829268292683</v>
+      </c>
       <c r="L70" t="n">
-        <v>72.81323877068559</v>
+        <v>71.3912394225983</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
+          <t>AQIFFA JAYA MANDIRI, CV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4223,15 +4223,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jl. Pelabuhan</t>
+          <t>Dusun Lamahu Desa Sipatana</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
+        <v>1347</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
+          <t>JAYA MANDIRI PERSADA, CV</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4240,20 +4240,18 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>100</v>
+        <v>68.08510638297872</v>
       </c>
       <c r="J71" t="n">
         <v>100</v>
       </c>
-      <c r="K71" t="n">
-        <v>96</v>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
-        <v>98.98039215686275</v>
+        <v>72.81323877068559</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4266,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EKA PUTRA, CV</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4278,15 +4276,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jalan Gagak, depan RM ASTA 6000, Desa Marisa Selatan, Kecamatan Marisa, Kabupaten Pohuwato</t>
+          <t>Jl. Pelabuhan</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1419</v>
+        <v>100</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>LOMAYA PUTRA, CV</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4295,18 +4293,20 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>75.86206896551724</v>
+        <v>100</v>
       </c>
       <c r="J72" t="n">
         <v>100</v>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>96</v>
+      </c>
       <c r="L72" t="n">
-        <v>81.54158215010142</v>
+        <v>98.98039215686275</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4321,43 +4321,41 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TRI SANDI YUDHA, PT</t>
+          <t>EKA PUTRA, CV</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jalan Jakarta, Kompleks Perum Griya Wiyan Lestari Blok D Nomor 1</t>
+          <t>Jalan Gagak, depan RM ASTA 6000, Desa Marisa Selatan, Kecamatan Marisa, Kabupaten Pohuwato</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>119</v>
+        <v>1419</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TRI SANDI YUDHA, PT</t>
+          <t>LOMAYA PUTRA, CV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>100</v>
+        <v>75.86206896551724</v>
       </c>
       <c r="J73" t="n">
         <v>100</v>
       </c>
-      <c r="K73" t="n">
-        <v>62.5</v>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>72.41379310344827</v>
+        <v>81.54158215010142</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4376,41 +4374,43 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARUMI, CV</t>
+          <t>TRI SANDI YUDHA, PT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>JALAN SAMRATULANGI DUSUN I TENGAH, DESA YOSONEGORO, KECAMATAN LIMBOTO BARAT, KABUPATEN GORONTALO</t>
+          <t>Jalan Jakarta, Kompleks Perum Griya Wiyan Lestari Blok D Nomor 1</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ARSA, CV</t>
+          <t>TRI SANDI YUDHA, PT</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>70.58823529411764</v>
+        <v>100</v>
       </c>
       <c r="J74" t="n">
         <v>100</v>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>62.5</v>
+      </c>
       <c r="L74" t="n">
-        <v>79.63800904977376</v>
+        <v>72.41379310344827</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DHARMA BAKTI, CV</t>
+          <t>ARUMI, CV</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4439,15 +4439,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JL. RAYA LIMBOTO NO. 9</t>
+          <t>JALAN SAMRATULANGI DUSUN I TENGAH, DESA YOSONEGORO, KECAMATAN LIMBOTO BARAT, KABUPATEN GORONTALO</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>421</v>
+        <v>265</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>RAHMAT ABADI, CV</t>
+          <t>ARSA, CV</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4456,14 +4456,14 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>68.75</v>
+        <v>70.58823529411764</v>
       </c>
       <c r="J75" t="n">
         <v>100</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>75</v>
+        <v>79.63800904977376</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4482,41 +4482,41 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GOMINA PERMAI INDAH, CV</t>
+          <t>DHARMA BAKTI, CV</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jalan Nani Wartabone</t>
+          <t>JL. RAYA LIMBOTO NO. 9</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1151</v>
+        <v>421</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>GLORIA INDAH, CV</t>
+          <t>RAHMAT ABADI, CV</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>71.7948717948718</v>
+        <v>68.75</v>
       </c>
       <c r="J76" t="n">
         <v>100</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
-        <v>75.97340930674264</v>
+        <v>75</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -4535,43 +4535,45 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ALIF SATYA PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>GOMINA PERMAI INDAH, CV</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DESA TINELO</t>
+          <t>Jalan Nani Wartabone</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>509</v>
+        <v>1151</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ALIF SETYA PERKASA, PT</t>
+          <t>GLORIA INDAH, CV</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>95.45454545454545</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>100</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>96.96969696969697</v>
+        <v>75.97340930674264</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4586,45 +4588,43 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MADINA MULTI KREASI, CV</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
+          <t>ALIF SATYA PERKASA, PT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>JALAN JARWADI LINGKUNGAN I</t>
+          <t>DESA TINELO</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>444</v>
+        <v>509</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SEMANGAT KARYA, CV</t>
+          <t>ALIF SETYA PERKASA, PT</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>63.41463414634146</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="J78" t="n">
-        <v>100</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>100</v>
+      </c>
       <c r="L78" t="n">
-        <v>68.83468834688347</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4639,45 +4639,43 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SELTA LESTARI, CV</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
+          <t>ALIF SATYA PERKASA, PT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dusun Teratai</t>
+          <t>DESA TINELO</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1434</v>
+        <v>509</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SINAR LESTARI, CV</t>
+          <t>ALIF SETYA PERKASA, PT</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>82.35294117647058</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
-      </c>
-      <c r="K79" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>100</v>
+      </c>
       <c r="L79" t="n">
-        <v>85.71428571428571</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4692,47 +4690,45 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GARUDA SAKTI, CV</t>
+          <t>MADINA MULTI KREASI, CV</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JALAN MATOLODULA</t>
+          <t>JALAN JARWADI LINGKUNGAN I</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2047</v>
+        <v>444</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>GARUDA SAKTI, CV</t>
+          <t>SEMANGAT KARYA, CV</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>100</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="J80" t="n">
         <v>100</v>
       </c>
-      <c r="K80" t="n">
-        <v>89.65517241379311</v>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
-        <v>95.40229885057471</v>
+        <v>68.83468834688347</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4747,41 +4743,41 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TULUS RAJAWALI GORONTALO, PT</t>
+          <t>SELTA LESTARI, CV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DESA TOTO SELATAN</t>
+          <t>Dusun Teratai</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1136</v>
+        <v>1434</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>KURNIA LOGISTIK PRATAMA, PT</t>
+          <t>SINAR LESTARI, CV</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>47.27272727272728</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="J81" t="n">
         <v>100</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
-        <v>53.86363636363637</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4800,45 +4796,47 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SINAR BATU ALAM, CV</t>
+          <t>GARUDA SAKTI, CV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jl. JENDRAL SUDIRMAN</t>
+          <t>JALAN MATOLODULA</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>246</v>
+        <v>2047</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SINAR ALINKO, CV</t>
+          <t>GARUDA SAKTI, CV</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>68.57142857142857</v>
+        <v>100</v>
       </c>
       <c r="J82" t="n">
         <v>100</v>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>89.65517241379311</v>
+      </c>
       <c r="L82" t="n">
-        <v>74.03726708074534</v>
+        <v>95.40229885057471</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4853,47 +4851,45 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PUTRA DEZA, CV</t>
+          <t>TULUS RAJAWALI GORONTALO, PT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DUSUN MUARA</t>
+          <t>DESA TOTO SELATAN</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>34</v>
+        <v>1136</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PUTRA DEZA, CV</t>
+          <t>KURNIA LOGISTIK PRATAMA, PT</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>100</v>
+        <v>47.27272727272728</v>
       </c>
       <c r="J83" t="n">
         <v>100</v>
       </c>
-      <c r="K83" t="n">
-        <v>90</v>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
-        <v>96.20689655172414</v>
+        <v>53.86363636363637</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4908,41 +4904,41 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ABADI JAYA BERSAMA NEW, CV</t>
+          <t>SINAR BATU ALAM, CV</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DESA BUNUYO KECAMATAN PAGUAT</t>
+          <t>Jl. JENDRAL SUDIRMAN</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1392</v>
+        <v>246</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CITRA ABDI KARYA, CV</t>
+          <t>SINAR ALINKO, CV</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>65.21739130434783</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="J84" t="n">
         <v>100</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
-        <v>69.85507246376811</v>
+        <v>74.03726708074534</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -4961,7 +4957,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARMADAN JAYA, CV</t>
+          <t>PUTRA DEZA, CV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4971,15 +4967,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jalan Hasan Dangkua Lingkungan I</t>
+          <t>DUSUN MUARA</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>275</v>
+        <v>34</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CAHAYA AGRO KARYA, CV</t>
+          <t>PUTRA DEZA, CV</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4988,18 +4984,20 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>64.86486486486487</v>
+        <v>100</v>
       </c>
       <c r="J85" t="n">
         <v>100</v>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>90</v>
+      </c>
       <c r="L85" t="n">
-        <v>71.8918918918919</v>
+        <v>96.20689655172414</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -5014,43 +5012,41 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SURYA SINTESIA, CV</t>
+          <t>ABADI JAYA BERSAMA NEW, CV</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>JALAN PADANG PERUMAHAN GRAHA 42 BLOK E NO.3</t>
+          <t>DESA BUNUYO KECAMATAN PAGUAT</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2214</v>
+        <v>1392</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SURYA SINTESIA, CV</t>
+          <t>CITRA ABDI KARYA, CV</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>100</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="J86" t="n">
         <v>100</v>
       </c>
-      <c r="K86" t="n">
-        <v>50.84745762711864</v>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>67.48370273794004</v>
+        <v>69.85507246376811</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -5069,41 +5065,41 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SENCIKA INDAH, CV</t>
+          <t>ARMADAN JAYA, CV</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jln. Pelabuhan Marisa</t>
+          <t>Jalan Hasan Dangkua Lingkungan I</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1442</v>
+        <v>275</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NUSA INDAH, CV</t>
+          <t>CAHAYA AGRO KARYA, CV</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>77.41935483870968</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="J87" t="n">
         <v>100</v>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
-        <v>81.72043010752688</v>
+        <v>71.8918918918919</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -5122,7 +5118,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
+          <t>SURYA SINTESIA, CV</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5132,15 +5128,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>JALAN CUT NYAK DIEN</t>
+          <t>JALAN PADANG PERUMAHAN GRAHA 42 BLOK E NO.3</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2194</v>
+        <v>2214</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
+          <t>SURYA SINTESIA, CV</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5155,14 +5151,14 @@
         <v>100</v>
       </c>
       <c r="K88" t="n">
-        <v>91.42857142857143</v>
+        <v>50.84745762711864</v>
       </c>
       <c r="L88" t="n">
-        <v>96.74285714285713</v>
+        <v>67.48370273794004</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5177,41 +5173,41 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SINAR PUTRI PRATAMA, CV</t>
+          <t>SENCIKA INDAH, CV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jalan PGRI</t>
+          <t>Jln. Pelabuhan Marisa</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>375</v>
+        <v>1442</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SINAR PURNAMA, CV</t>
+          <t>NUSA INDAH, CV</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>75</v>
+        <v>77.41935483870968</v>
       </c>
       <c r="J89" t="n">
         <v>100</v>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
-        <v>78.70370370370371</v>
+        <v>81.72043010752688</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -5230,45 +5226,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BAYOORS, CV</t>
+          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jl. -</t>
+          <t>JALAN CUT NYAK DIEN</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1139</v>
+        <v>2194</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CITOS, CV</t>
+          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J90" t="n">
         <v>100</v>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>91.42857142857143</v>
+      </c>
       <c r="L90" t="n">
-        <v>70.66666666666667</v>
+        <v>96.74285714285713</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5281,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KARYA JAYA BERSAMA, CV</t>
+          <t>SINAR PUTRI PRATAMA, CV</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5293,15 +5291,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dusun Motolohu</t>
+          <t>Jalan PGRI</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>KARYA BERSAMA, CV</t>
+          <t>SINAR PURNAMA, CV</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5310,16 +5308,14 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>87.17948717948718</v>
+        <v>75</v>
       </c>
       <c r="J91" t="n">
         <v>100</v>
       </c>
-      <c r="K91" t="n">
-        <v>27.45098039215686</v>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
-        <v>67.55656108597285</v>
+        <v>78.70370370370371</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -5338,43 +5334,41 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ALYA BERKAH, CV</t>
+          <t>BAYOORS, CV</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jalan Kancil</t>
+          <t>Jl. -</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>158</v>
+        <v>1139</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>CITOS, CV</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="J92" t="n">
         <v>100</v>
       </c>
-      <c r="K92" t="n">
-        <v>85.71428571428572</v>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>78.34101382488478</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -5393,7 +5387,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INDAH RAHAYU, CV</t>
+          <t>KARYA JAYA BERSAMA, CV</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5403,15 +5397,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
+          <t>Dusun Motolohu</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INDAH KERAMIK, CV</t>
+          <t>KARYA BERSAMA, CV</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5420,14 +5414,16 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>72.72727272727273</v>
+        <v>87.17948717948718</v>
       </c>
       <c r="J93" t="n">
         <v>100</v>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>27.45098039215686</v>
+      </c>
       <c r="L93" t="n">
-        <v>78.18181818181819</v>
+        <v>67.55656108597285</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -5446,41 +5442,41 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NURUL YAKIN, CV</t>
+          <t>INDAH RAHAYU, CV</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jln. Sultan Amai</t>
+          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1431</v>
+        <v>291</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>RIDWAN, CV</t>
+          <t>INDAH KERAMIK, CV</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>56.00000000000001</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="J94" t="n">
         <v>100</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>65.26315789473684</v>
+        <v>78.18181818181819</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -5499,41 +5495,41 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WAHYU, CV</t>
+          <t>NURUL YAKIN, CV</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jl. Kesehatan, Desa Toto Utara</t>
+          <t>Jln. Sultan Amai</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1160</v>
+        <v>1431</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>JDS RAYA, CV</t>
+          <t>RIDWAN, CV</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>57.14285714285714</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>100</v>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
-        <v>70.32967032967032</v>
+        <v>65.26315789473684</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -5552,47 +5548,45 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
+          <t>WAHYU, CV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>JALAN PALMA</t>
+          <t>Jl. Kesehatan, Desa Toto Utara</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2098</v>
+        <v>1160</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
+          <t>JDS RAYA, CV</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>100</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="J96" t="n">
         <v>100</v>
       </c>
-      <c r="K96" t="n">
-        <v>44.99999999999999</v>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>84.875</v>
+        <v>70.32967032967032</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5607,45 +5601,47 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CAHAYA BULAN, CV</t>
+          <t>SUNGAI BONE GORONTALO, CV</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dusun Lamahu</t>
+          <t>JALAN PALMA</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>414</v>
+        <v>2098</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CAHAYA AGUNG, CV</t>
+          <t>SUNGAI BONE GORONTALO, CV</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="J97" t="n">
         <v>100</v>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>44.99999999999999</v>
+      </c>
       <c r="L97" t="n">
-        <v>85</v>
+        <v>84.875</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -5660,47 +5656,45 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ALLIESSAN, PT</t>
+          <t>CAHAYA BULAN, CV</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>JL. SULTAN HASANUDDIN</t>
+          <t>Dusun Lamahu</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2240</v>
+        <v>414</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ALLIESSAN, PT</t>
+          <t>CAHAYA AGUNG, CV</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>81.25</v>
       </c>
       <c r="J98" t="n">
         <v>100</v>
       </c>
-      <c r="K98" t="n">
-        <v>95</v>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>97.23684210526316</v>
+        <v>85</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5709,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
+          <t>ALLIESSAN, PT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5725,15 +5719,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jalan Beringin</t>
+          <t>JL. SULTAN HASANUDDIN</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1683</v>
+        <v>2240</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
+          <t>ALLIESSAN, PT</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5748,10 +5742,10 @@
         <v>100</v>
       </c>
       <c r="K99" t="n">
-        <v>50.90909090909091</v>
+        <v>95</v>
       </c>
       <c r="L99" t="n">
-        <v>83.63636363636364</v>
+        <v>97.23684210526316</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -5770,45 +5764,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ZIITEK, CV</t>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
+          <t>Jalan Beringin</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1208</v>
+        <v>1683</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SPEKTEK, CV</t>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>66.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="J100" t="n">
         <v>100</v>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>50.90909090909091</v>
+      </c>
       <c r="L100" t="n">
-        <v>76.19047619047619</v>
+        <v>83.63636363636364</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -5823,41 +5819,41 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USAHA SEJAHTERA, CV</t>
+          <t>ZIITEK, CV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jl. Pelabuhan</t>
+          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1404</v>
+        <v>1208</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BRESCIA SEJAHTERA SELATAN, PT</t>
+          <t>SPEKTEK, CV</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J101" t="n">
         <v>100</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
-        <v>69.02173913043478</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -5876,41 +5872,41 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TRIANA, CV</t>
+          <t>USAHA SEJAHTERA, CV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Perum Azizah Permai Blok I Nomor 3</t>
+          <t>Jl. Pelabuhan</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>364</v>
+        <v>1404</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
+          <t>BRESCIA SEJAHTERA SELATAN, PT</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>78.26086956521739</v>
+        <v>62.5</v>
       </c>
       <c r="J102" t="n">
         <v>100</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>84.47204968944099</v>
+        <v>69.02173913043478</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -5929,7 +5925,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BINTANG ADZKIA, CV</t>
+          <t>TRIANA, CV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5939,15 +5935,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jalan A. Otoluwa</t>
+          <t>Perum Azizah Permai Blok I Nomor 3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>263</v>
+        <v>364</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ANUGERAH ABADI, CV</t>
+          <t>PRIMADONA, CV</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5956,14 +5952,14 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>61.11111111111111</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="J103" t="n">
         <v>100</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>68.18181818181819</v>
+        <v>84.47204968944099</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -5974,49 +5970,49 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>lpse</t>
+          <t>sijk</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HADFIR PERKASA, CV</t>
+          <t>BINTANG ADZKIA, CV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
+          <t>Jalan A. Otoluwa</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>844</v>
+        <v>263</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DWI AULIA PERKASA, CV</t>
+          <t>ANUGERAH ABADI, CV</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>71.7948717948718</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="J104" t="n">
         <v>100</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
-        <v>76.92307692307692</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -6031,45 +6027,45 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TULUS MULIA, CV</t>
+          <t>HADFIR PERKASA, CV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
+          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1906</v>
+        <v>844</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>LIMA SATU, CV</t>
+          <t>DWI AULIA PERKASA, CV</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>64.28571428571428</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="J105" t="n">
         <v>100</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
-        <v>71.80451127819549</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6084,45 +6080,45 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DWI SAMA, CV</t>
+          <t>TULUS MULIA, CV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>DESA TALANGO KECAMATAN KABILA</t>
+          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1408</v>
+        <v>1906</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRAHMATI, CV</t>
+          <t>LIMA SATU, CV</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>72</v>
+        <v>64.28571428571428</v>
       </c>
       <c r="J106" t="n">
         <v>100</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
-        <v>79</v>
+        <v>71.80451127819549</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -6137,47 +6133,45 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AZRAM MAJU BERSAMA, CV</t>
+          <t>DWI SAMA, CV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
+          <t>DESA TALANGO KECAMATAN KABILA</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>145</v>
+        <v>1408</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>AZRAM MAJU BERSAMA, CV</t>
+          <t>DIRAHMATI, CV</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J107" t="n">
         <v>100</v>
       </c>
-      <c r="K107" t="n">
-        <v>42.30769230769231</v>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
-        <v>66.89785624211854</v>
+        <v>79</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -6192,34 +6186,34 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
+          <t>AZRAM MAJU BERSAMA, CV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
+          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1400</v>
+        <v>145</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
+          <t>AZRAM MAJU BERSAMA, CV</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6228,13 +6222,15 @@
       <c r="J108" t="n">
         <v>100</v>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>42.30769230769231</v>
+      </c>
       <c r="L108" t="n">
-        <v>100</v>
+        <v>66.89785624211854</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -6245,51 +6241,49 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BINTANG PALMA, CV</t>
+          <t>AMIN, CV</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
+          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1955</v>
+        <v>1400</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ADI CIPTA UTAMAI, CV</t>
+          <t>AMIN, CV</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>59.45945945945945</v>
+        <v>100</v>
       </c>
       <c r="J109" t="n">
         <v>100</v>
       </c>
-      <c r="K109" t="n">
-        <v>55.67010309278351</v>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
-        <v>59.12351231938861</v>
+        <v>100</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6300,11 +6294,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MITRA CAHAYA TANAMON, CV</t>
+          <t>BINTANG PALMA, CV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6314,7 +6308,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
+          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6331,16 +6325,16 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>50</v>
+        <v>59.45945945945945</v>
       </c>
       <c r="J110" t="n">
         <v>100</v>
       </c>
       <c r="K110" t="n">
-        <v>68.08510638297872</v>
+        <v>55.67010309278351</v>
       </c>
       <c r="L110" t="n">
-        <v>63.94479585968948</v>
+        <v>59.12351231938861</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -6355,45 +6349,47 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RIZKY ADITYA PRATAMA, CV</t>
+          <t>MITRA CAHAYA TANAMON, CV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Desa Tanah Putih Kecamatan Botupingge</t>
+          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1492</v>
+        <v>1955</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>TITIAN PRATAMA, CV</t>
+          <t>ADI CIPTA UTAMAI, CV</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>61.90476190476191</v>
+        <v>50</v>
       </c>
       <c r="J111" t="n">
         <v>100</v>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>68.08510638297872</v>
+      </c>
       <c r="L111" t="n">
-        <v>67.34693877551021</v>
+        <v>63.94479585968948</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -6408,45 +6404,45 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ARITO PRATAMA, CV</t>
+          <t>RIZKY ADITYA PRATAMA, CV</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>JL. TRANS SULAWESI DESA MOLOMBULAHE KECAMATAN PAGUYAMAN</t>
+          <t>Desa Tanah Putih Kecamatan Botupingge</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>251</v>
+        <v>1492</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ARYA PRATAMA, CV</t>
+          <t>TITIAN PRATAMA, CV</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>84.84848484848484</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="J112" t="n">
         <v>100</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
-        <v>87.73448773448773</v>
+        <v>67.34693877551021</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -6461,45 +6457,45 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ANUGERAH BERSAMA, CV</t>
+          <t>ARITO PRATAMA, CV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jln Basoe Bobihoe</t>
+          <t>JL. TRANS SULAWESI DESA MOLOMBULAHE KECAMATAN PAGUYAMAN</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>828</v>
+        <v>251</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>BERKAH ANUGRAH, CV</t>
+          <t>ARYA PRATAMA, CV</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>78.94736842105263</v>
+        <v>84.84848484848484</v>
       </c>
       <c r="J113" t="n">
         <v>100</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>82.45614035087719</v>
+        <v>87.73448773448773</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -6514,51 +6510,49 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ARVID, CV</t>
+          <t>ANUGERAH BERSAMA, CV</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jln. Jambura</t>
+          <t>Jln Basoe Bobihoe</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>157</v>
+        <v>828</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ARVID, CV</t>
+          <t>BERKAH ANUGRAH, CV</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>100</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="J114" t="n">
         <v>100</v>
       </c>
-      <c r="K114" t="n">
-        <v>90.90909090909091</v>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
-        <v>95.63636363636364</v>
+        <v>82.45614035087719</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -6569,34 +6563,34 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
+          <t>ARVID, CV</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Desa Limbato Kec. Tilamuta</t>
+          <t>Jln. Jambura</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>364</v>
+        <v>157</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
+          <t>ARVID, CV</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6605,9 +6599,11 @@
       <c r="J115" t="n">
         <v>100</v>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>90.90909090909091</v>
+      </c>
       <c r="L115" t="n">
-        <v>100</v>
+        <v>95.63636363636364</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -6622,11 +6618,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
+          <t>PRIMADONA, CV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6636,15 +6632,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
+          <t>Desa Limbato Kec. Tilamuta</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>267</v>
+        <v>364</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>BAROKAH ABADI, CV</t>
+          <t>PRIMADONA, CV</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6653,18 +6649,18 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>62.06896551724138</v>
+        <v>100</v>
       </c>
       <c r="J116" t="n">
         <v>100</v>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
-        <v>71.55172413793103</v>
+        <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6675,47 +6671,45 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SATYA HARDANA, CV</t>
+          <t>ALL AHAD, CV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
+          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SATYA HARDANA, CV</t>
+          <t>BAROKAH ABADI, CV</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>100</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="J117" t="n">
         <v>100</v>
       </c>
-      <c r="K117" t="n">
-        <v>53.84615384615385</v>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
-        <v>71.15384615384616</v>
+        <v>71.55172413793103</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -6730,11 +6724,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>SATYA HARDANA, CV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6744,15 +6738,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
+          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1933</v>
+        <v>138</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DAR AL TAUHID, CV</t>
+          <t>SATYA HARDANA, CV</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6761,14 +6755,16 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J118" t="n">
         <v>100</v>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>53.84615384615385</v>
+      </c>
       <c r="L118" t="n">
-        <v>60.52631578947368</v>
+        <v>71.15384615384616</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -6783,45 +6779,45 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FELQIMUN ADIJAYA, CV</t>
+          <t>RARA BERKAH, CV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
+          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>758</v>
+        <v>1933</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ADHITYA, CV</t>
+          <t>DAR AL TAUHID, CV</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>58.06451612903225</v>
+        <v>50</v>
       </c>
       <c r="J119" t="n">
         <v>100</v>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>65.05376344086021</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -6836,49 +6832,49 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ANTARIKSA PERSADA, CV</t>
+          <t>FELQIMUN ADIJAYA, CV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
+          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1226</v>
+        <v>758</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ANTARIKSA PERSADA, CV</t>
+          <t>ADHITYA, CV</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>100</v>
+        <v>58.06451612903225</v>
       </c>
       <c r="J120" t="n">
         <v>100</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>100</v>
+        <v>65.05376344086021</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -6889,49 +6885,102 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>16</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ANTARIKSA PERSADA, CV</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ANTARIKSA PERSADA, CV</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>100</v>
+      </c>
+      <c r="J121" t="n">
+        <v>100</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>100</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>lpse</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
         <v>17</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>SEXY ROAD INDO, CV</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>7502</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>Perum Asabri Blok E no 3, Ulapato A</t>
         </is>
       </c>
-      <c r="F121" t="n">
+      <c r="F122" t="n">
         <v>55</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>SEXY ROAD INDO, CV</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>7502</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>100</v>
-      </c>
-      <c r="J121" t="n">
-        <v>100</v>
-      </c>
-      <c r="K121" t="n">
+      <c r="I122" t="n">
+        <v>100</v>
+      </c>
+      <c r="J122" t="n">
+        <v>100</v>
+      </c>
+      <c r="K122" t="n">
         <v>77.41935483870968</v>
       </c>
-      <c r="L121" t="n">
+      <c r="L122" t="n">
         <v>86.13469156762875</v>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>

--- a/monitoring_weighted_similarity.xlsx
+++ b/monitoring_weighted_similarity.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>source_row_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source_kdkab</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source_address</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>matched_sf_index</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sf_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sf_kdkab</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sf_address</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sim_name</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sim_kab</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sim_address</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>weighted_similarity</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>decision</t>
         </is>
@@ -508,11 +525,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SINAR SARI, CV</t>
+          <t>EVANTO LESTARI, CV</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,17 +537,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>73.68421052631579</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>jl merpati, nomor 155</t>
+        </is>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
       <c r="L2" t="n">
-        <v>77.4436090225564</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47.39130434782609</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -573,19 +597,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>62.22222222222222</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>jl sultan botutihe kota timur heledulaa selatan</t>
+        </is>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>92.30769230769231</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>77.88034188034187</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -628,21 +657,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>100</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>jl palma dungingi libuo</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>57.14285714285714</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>78.02197802197801</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -671,11 +705,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2126</v>
+        <v>1730</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>USAHA MANDIRI, CV</t>
+          <t>SINAR JAYA, CV</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -683,19 +717,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>52.38095238095239</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jl taman bunga 4 kota timur moodu</t>
+        </is>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>71.69811320754718</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>65.43164755508856</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>46.51162790697674</v>
+      </c>
+      <c r="M5" t="n">
+        <v>48.22739018087855</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -738,19 +777,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>100</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jl tinaloga kota utara dulomo selatan</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>95.57894736842105</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -781,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PUTRA MITRA PERKASA, CV</t>
+          <t>PUTRA MAULANA, CV</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -793,17 +837,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>73.46938775510203</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>marisa marisa utara</t>
+        </is>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
       <c r="L7" t="n">
-        <v>77.00680272108842</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="M7" t="n">
+        <v>47.52056404230318</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -846,19 +897,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>100</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>jl raden saleh kota selatan limba u dua</t>
+        </is>
       </c>
       <c r="J8" t="n">
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>90.32258064516128</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>96.6425279789335</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -901,21 +957,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>100</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>jl hb jassin kota selatan limba u satu</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>46.15384615384615</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>77.82805429864254</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>21.05263157894737</v>
+      </c>
+      <c r="M9" t="n">
+        <v>73.68421052631579</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -944,11 +1005,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KUMALA JAYA, CV</t>
+          <t>TEHNIK RAYA, CV</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -956,17 +1017,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>75.86206896551724</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>tilamuta limbato</t>
+        </is>
       </c>
       <c r="J10" t="n">
-        <v>100</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
       <c r="L10" t="n">
-        <v>81.22605363984674</v>
-      </c>
-      <c r="M10" t="inlineStr">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="M10" t="n">
+        <v>53.18181818181817</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -997,11 +1065,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>406</v>
+        <v>29</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FAJAR MANDIRI, CV</t>
+          <t>BINTANG TELAGA MURNI, PT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1009,17 +1077,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>70</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>jl husin bilondatu nomor 37 kabupaten gorontalo</t>
+        </is>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
       <c r="L11" t="n">
-        <v>74.44444444444444</v>
-      </c>
-      <c r="M11" t="inlineStr">
+        <v>70.4225352112676</v>
+      </c>
+      <c r="M11" t="n">
+        <v>49.74934351873955</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1062,19 +1137,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>100</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>dsn ii</t>
+        </is>
       </c>
       <c r="J12" t="n">
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>85.71428571428572</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>96.73469387755102</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="M12" t="n">
+        <v>96.31336405529954</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1105,11 +1185,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PUTRA POSEIDON, CV</t>
+          <t>PUTRA, CV</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1117,17 +1197,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>72.72727272727273</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>limboto barat yoosonegoro</t>
+        </is>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
       <c r="L13" t="n">
-        <v>78.4688995215311</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>12.90322580645162</v>
+      </c>
+      <c r="M13" t="n">
+        <v>57.6549073732719</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1158,11 +1245,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>776</v>
+        <v>908</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HAYUTAMA KONSTRUKSINDO, CV</t>
+          <t>MANDIRI JAYA ABADI, CV</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1170,17 +1257,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>70.58823529411764</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi limboto barat pone</t>
+        </is>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
       <c r="L14" t="n">
-        <v>74.64503042596348</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="M14" t="n">
+        <v>59.24371806722689</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1211,11 +1305,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>973</v>
+        <v>48</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BINTANG NUSANTARA, CV</t>
+          <t>MHASTER EDRIS NUSANTARA, CV</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1223,17 +1317,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>71.42857142857143</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>dsn melito</t>
+        </is>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
       <c r="L15" t="n">
-        <v>76</v>
-      </c>
-      <c r="M15" t="inlineStr">
+        <v>58.8235294117647</v>
+      </c>
+      <c r="M15" t="n">
+        <v>53.27731092436975</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1264,11 +1365,11 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1141</v>
+        <v>1192</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CITRA NUSANTARA, CV</t>
+          <t>REKSINAR PERKASA, CV</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1276,17 +1377,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>53.06122448979591</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>lemito lemito utara</t>
+        </is>
       </c>
       <c r="J16" t="n">
-        <v>100</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
       <c r="L16" t="n">
-        <v>58.58343337334934</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>72.72727272727272</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.18181818181818</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1317,11 +1425,11 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>455</v>
+        <v>18</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MALIKA KONSTRUKSI, CV</t>
+          <t>GANITEK KONSTRUKSI, CV</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1329,19 +1437,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>79.06976744186046</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>lingk i</t>
+        </is>
       </c>
       <c r="J17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
-        <v>22.72727272727273</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>68.27509016291506</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="M17" t="n">
+        <v>50.44444444444445</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1372,11 +1485,11 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BERKAH ANNUR MARISA, PT</t>
+          <t>KHAIRUNNISA KARYA HULAWA, PT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1384,19 +1497,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>37.83783783783784</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi</t>
+        </is>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97.14285714285714</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>74.3972543972544</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1427,11 +1545,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>984</v>
+        <v>53</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ARIES PRATAMA TEKNIK, CV</t>
+          <t>SINAR AGUNG TANGGUH, PT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1439,17 +1557,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>73.17073170731707</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>dsn gompase induk</t>
+        </is>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
       <c r="L19" t="n">
-        <v>78.28106852497096</v>
-      </c>
-      <c r="M19" t="inlineStr">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="M19" t="n">
+        <v>60.95679012345678</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1492,19 +1617,24 @@
           <t>7505</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>88.88888888888889</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>dsn payunga kwandang titidu</t>
+        </is>
       </c>
       <c r="J20" t="n">
-        <v>100</v>
+        <v>66.66670000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>38.09523809523809</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>76.01410934744268</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>6.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>60.41668888888889</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1547,19 +1677,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>100</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>dsn i mekar sari</t>
+        </is>
       </c>
       <c r="J21" t="n">
         <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>94.11764705882352</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>97.59358288770053</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>94.11764705882354</v>
+      </c>
+      <c r="M21" t="n">
+        <v>97.35294117647058</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1602,17 +1737,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>83.72093023255813</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>popayato barat tunas jaya</t>
+        </is>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100</v>
+      </c>
       <c r="L22" t="n">
-        <v>85.96631916599839</v>
-      </c>
-      <c r="M22" t="inlineStr">
+        <v>18.18181818181819</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67.43801652892562</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1655,19 +1797,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>60.31746031746032</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>jl pelabuhan</t>
+        </is>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
+        <v>28.5714</v>
       </c>
       <c r="K23" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>72.55291005291006</v>
-      </c>
-      <c r="M23" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>53.00749999999999</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1710,19 +1857,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>66.66666666666667</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>jl sawit 1 kota barat buladu</t>
+        </is>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>66.66670000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>65.71428571428571</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="M24" t="n">
+        <v>60.49384814814815</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1753,11 +1905,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1803</v>
+        <v>144</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GALANG PERDANA, CV</t>
+          <t>IPUZAN PRATAMA KONSTRUKSI, CV</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1765,19 +1917,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>41.17647058823529</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>jl bandes</t>
+        </is>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>50.52631578947368</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>51.13767292393307</v>
-      </c>
-      <c r="M25" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M25" t="n">
+        <v>74.46808510638297</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1808,11 +1965,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2245</v>
+        <v>127</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DALIA PERSADA, CV</t>
+          <t>AMSON, CV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1820,19 +1977,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>55.55555555555556</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>jl bali nomor 71</t>
+        </is>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>59.15492957746478</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>60.82145896823436</v>
-      </c>
-      <c r="M26" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>68.08510638297872</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1863,11 +2025,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>305</v>
+        <v>428</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MIWAN STAR, CV</t>
+          <t>LINTANG GEMILANG, CV</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1875,17 +2037,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>62.5</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>jl mutiara no 241 paguyaman wonggahu</t>
+        </is>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
       <c r="L27" t="n">
-        <v>69.31818181818181</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="M27" t="n">
+        <v>49.5475113122172</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1928,17 +2097,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>76.47058823529412</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>tilamuta hungayonaa</t>
+        </is>
       </c>
       <c r="J28" t="n">
-        <v>100</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="K28" t="n">
+        <v>100</v>
+      </c>
       <c r="L28" t="n">
-        <v>80.23529411764706</v>
-      </c>
-      <c r="M28" t="inlineStr">
+        <v>17.39130434782609</v>
+      </c>
+      <c r="M28" t="n">
+        <v>73.18260869565218</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -1969,11 +2145,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1187</v>
+        <v>1078</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PRIMA JAYA, CV</t>
+          <t>SYANUH JAYA, CV</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1981,17 +2157,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>57.14285714285714</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>marisa marisa selatan</t>
+        </is>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
       <c r="L29" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="M29" t="inlineStr">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="M29" t="n">
+        <v>51.14035087719299</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2022,11 +2205,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1488</v>
+        <v>1351</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SINAR PERMATA, CV</t>
+          <t>BONE RAYA PERKASA, CV</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2034,17 +2217,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>63.41463414634146</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>kabila padengo</t>
+        </is>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
       <c r="L30" t="n">
-        <v>68.6411149825784</v>
-      </c>
-      <c r="M30" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="M30" t="n">
+        <v>26.51428571428572</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2075,11 +2265,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1824</v>
+        <v>133</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>KARYA BERSAMA, CV</t>
+          <t>RIZKA RIZKI BAROKAH, CV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2087,19 +2277,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>60</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>jl palma</t>
+        </is>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>84.21052631578947</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>75.22556390977444</v>
-      </c>
-      <c r="M31" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2130,11 +2325,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1693</v>
+        <v>1732</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LINGGA PRATAMA, CV</t>
+          <t>SINAR UTAMA, CV</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2142,19 +2337,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>jl taman indah kota timur moodu</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>50</v>
       </c>
-      <c r="J32" t="n">
-        <v>100</v>
-      </c>
       <c r="K32" t="n">
-        <v>73.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>67.38738738738739</v>
-      </c>
-      <c r="M32" t="inlineStr">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="M32" t="n">
+        <v>54.98533724340177</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2185,11 +2385,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RITNI LESTARI, CV</t>
+          <t>SURYA INDAH, CV</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2197,17 +2397,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>55.55555555555556</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>jl sudirman tilamuta limbato</t>
+        </is>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
       <c r="L33" t="n">
-        <v>63.28502415458938</v>
-      </c>
-      <c r="M33" t="inlineStr">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="M33" t="n">
+        <v>31.34920634920634</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2238,11 +2445,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1735</v>
+        <v>2014</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BRAWIJAYA SAKTI, CV</t>
+          <t>AGUNG RAYA, CV</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2250,21 +2457,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>42.42424242424242</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi</t>
+        </is>
       </c>
       <c r="J34" t="n">
         <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>63.95316804407714</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>32</v>
+      </c>
+      <c r="M34" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -2305,19 +2517,24 @@
           <t>7505</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>100</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>desa molinhkapoto kwandang molingkapoto</t>
+        </is>
       </c>
       <c r="J35" t="n">
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>94.11764705882352</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="M35" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M35" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -2348,11 +2565,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>337</v>
+        <v>37</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TEGAR GITA PRATAMA, CV</t>
+          <t>BESTARI MULYA, CV</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2360,17 +2577,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>74.41860465116279</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>jl bontula</t>
+        </is>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
       <c r="L36" t="n">
-        <v>78.51162790697674</v>
-      </c>
-      <c r="M36" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2401,11 +2625,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>925</v>
+        <v>45</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>YENTRI JAYA, CV</t>
+          <t>NABHAN PUTRA, CV</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2413,17 +2637,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>58.06451612903225</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi</t>
+        </is>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>100</v>
+      </c>
       <c r="L37" t="n">
-        <v>66.45161290322581</v>
-      </c>
-      <c r="M37" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="M37" t="n">
+        <v>34.37037037037037</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2466,19 +2697,24 @@
           <t>7505</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>100</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi atinggola kotajin utara</t>
+        </is>
       </c>
       <c r="J38" t="n">
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>91.89189189189189</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>96.04482531311798</v>
-      </c>
-      <c r="M38" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M38" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -2509,11 +2745,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUFNAZ, CV</t>
+          <t>MULYA DHARMA NUSA, PT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2521,17 +2757,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>72.72727272727273</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>jl mbui bungale no 363</t>
+        </is>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>100</v>
+      </c>
       <c r="L39" t="n">
-        <v>79.54545454545455</v>
-      </c>
-      <c r="M39" t="inlineStr">
+        <v>64.28571428571428</v>
+      </c>
+      <c r="M39" t="n">
+        <v>51.0204081632653</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2562,11 +2805,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>271</v>
+        <v>391</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BINA PRATAMA, CV</t>
+          <t>BINTANG GALAXI, CV</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2574,17 +2817,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>70</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>paguyaman pantai bubaa</t>
+        </is>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K40" t="n">
+        <v>100</v>
+      </c>
       <c r="L40" t="n">
-        <v>74.28571428571429</v>
-      </c>
-      <c r="M40" t="inlineStr">
+        <v>35.29411764705883</v>
+      </c>
+      <c r="M40" t="n">
+        <v>45.09803921568627</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2627,19 +2877,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>100</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>jl muchlis rahim</t>
+        </is>
       </c>
       <c r="J41" t="n">
         <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>91.42857142857143</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>95.71428571428571</v>
-      </c>
-      <c r="M41" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M41" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -2670,11 +2925,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AAVAIRO MANDIRI JAYA, CV</t>
+          <t>VIEKMA MANDIRI, CV</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2682,17 +2937,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>57.69230769230769</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>dsn towayu paguyaman pantai towayu</t>
+        </is>
       </c>
       <c r="J42" t="n">
-        <v>100</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K42" t="n">
+        <v>100</v>
+      </c>
       <c r="L42" t="n">
-        <v>62.98076923076923</v>
-      </c>
-      <c r="M42" t="inlineStr">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="M42" t="n">
+        <v>45.3890824622532</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2735,19 +2997,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>100</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>jl karim mahmud</t>
+        </is>
       </c>
       <c r="J43" t="n">
         <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>90.90909090909091</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>96.44268774703556</v>
-      </c>
-      <c r="M43" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M43" t="n">
+        <v>100</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -2778,11 +3045,11 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1119</v>
+        <v>1078</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ANTARIKSA JAYA, CV</t>
+          <t>SYANUH JAYA, CV</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2790,17 +3057,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>60</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>marisa marisa selatan</t>
+        </is>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K44" t="n">
+        <v>100</v>
+      </c>
       <c r="L44" t="n">
-        <v>66.15384615384616</v>
-      </c>
-      <c r="M44" t="inlineStr">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="M44" t="n">
+        <v>63.59882005899704</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2843,19 +3117,24 @@
           <t>7505</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>100</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>dsn mangrove kwandang katialada</t>
+        </is>
       </c>
       <c r="J45" t="n">
         <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>92.30769230769231</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>97.00854700854701</v>
-      </c>
-      <c r="M45" t="inlineStr">
+        <v>72.72727272727272</v>
+      </c>
+      <c r="M45" t="n">
+        <v>88.06818181818181</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -2886,11 +3165,11 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1400</v>
+        <v>1443</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
+          <t>CAHAYA AGUNG, CV</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2898,17 +3177,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>70</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>desa marisa selatan</t>
+        </is>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100</v>
+      </c>
       <c r="L46" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="M46" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M46" t="n">
+        <v>52.55813953488372</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2939,11 +3225,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>694</v>
+        <v>755</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BINTANG FAJAR NUSANTARA, CV</t>
+          <t>MUTHIA SARI, CV</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2951,17 +3237,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>65.38461538461539</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>mootilango paris</t>
+        </is>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
-      </c>
-      <c r="K47" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K47" t="n">
+        <v>100</v>
+      </c>
       <c r="L47" t="n">
-        <v>70.15915119363396</v>
-      </c>
-      <c r="M47" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="M47" t="n">
+        <v>49.1764705882353</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -2992,11 +3285,11 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>458</v>
+        <v>250</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MAWIRNA INDAH, CV</t>
+          <t>MITRA PERDANA, CV</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3004,17 +3297,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>60.86956521739131</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>paguyaman girisa</t>
+        </is>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K48" t="n">
+        <v>100</v>
+      </c>
       <c r="L48" t="n">
-        <v>65.61264822134387</v>
-      </c>
-      <c r="M48" t="inlineStr">
+        <v>48.27586206896552</v>
+      </c>
+      <c r="M48" t="n">
+        <v>48.27586206896552</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3045,29 +3345,36 @@
         </is>
       </c>
       <c r="F49" t="n">
+        <v>29</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>BINTANG TELAGA MURNI, PT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>jl husin bilondatu nomor 37 kabupaten gorontalo</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>MARKA INDAH, CV</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>70.27027027027026</v>
-      </c>
-      <c r="J49" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>100</v>
+      </c>
       <c r="L49" t="n">
-        <v>74.84407484407484</v>
-      </c>
-      <c r="M49" t="inlineStr">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="M49" t="n">
+        <v>49.37888198757764</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3098,11 +3405,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>470</v>
+        <v>406</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DUTA MANDIRI, CV</t>
+          <t>FAJAR MANDIRI, CV</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3110,19 +3417,26 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>90.32258064516128</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>mananggu salilama</t>
+        </is>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K50" t="n">
+        <v>100</v>
+      </c>
       <c r="L50" t="n">
-        <v>92.35993208828522</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>DROP</t>
+        <v>35.71428571428571</v>
+      </c>
+      <c r="M50" t="n">
+        <v>51.64835164835164</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3151,11 +3465,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1933</v>
+        <v>165</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DAR AL TAUHID, CV</t>
+          <t>CAHAYA TIMUR SINANDAHA, PT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3163,17 +3477,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>55.31914893617022</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>kota gorontalo</t>
+        </is>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>100</v>
+      </c>
       <c r="L51" t="n">
-        <v>60.57571964956196</v>
-      </c>
-      <c r="M51" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M51" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3204,11 +3525,11 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1188</v>
+        <v>1254</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PURNAMA JAYA, CV</t>
+          <t>PRATAMA ERLANGGA JAYA, CV</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3216,17 +3537,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>64.86486486486487</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>dsn anggrek marisa marisa utara</t>
+        </is>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K52" t="n">
+        <v>100</v>
+      </c>
       <c r="L52" t="n">
-        <v>70.4864864864865</v>
-      </c>
-      <c r="M52" t="inlineStr">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="M52" t="n">
+        <v>57.73811294642857</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3257,11 +3585,11 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2222</v>
+        <v>169</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ALFA INDORAYA, CV</t>
+          <t>AFANDY INDO GRUP, PT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3269,19 +3597,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>57.14285714285714</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>jl beringin, perum bele olando blok d.31</t>
+        </is>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>33.3333</v>
       </c>
       <c r="K53" t="n">
-        <v>54.05405405405406</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>59.49455949455949</v>
-      </c>
-      <c r="M53" t="inlineStr">
+        <v>68.9655172413793</v>
+      </c>
+      <c r="M53" t="n">
+        <v>58.83813588070829</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3312,11 +3645,11 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MARKA INDAH, CV</t>
+          <t>DWI INDO CIPTA, CV</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3324,17 +3657,18 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>60.60606060606061</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>100</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>67.76859504132231</v>
-      </c>
-      <c r="M54" t="inlineStr">
+        <v>33.3333</v>
+      </c>
+      <c r="K54" t="n">
+        <v>100</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>48.14812222222222</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3377,19 +3711,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>100</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>jl rusli datau 1 perum alya iii blok b nomor 2</t>
+        </is>
       </c>
       <c r="J55" t="n">
         <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>92.92929292929293</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>94.72186655285246</v>
-      </c>
-      <c r="M55" t="inlineStr">
+        <v>94.28571428571429</v>
+      </c>
+      <c r="M55" t="n">
+        <v>95.85434173669469</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3420,11 +3759,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1191</v>
+        <v>1091</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PUTRA MITRA PERKASA, CV</t>
+          <t>TRI TUNGGAL PERKASA, CV</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3432,17 +3771,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>65.21739130434783</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>buntulia taluduyunu</t>
+        </is>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K56" t="n">
+        <v>100</v>
+      </c>
       <c r="L56" t="n">
-        <v>70.37037037037037</v>
-      </c>
-      <c r="M56" t="inlineStr">
+        <v>32.25806451612904</v>
+      </c>
+      <c r="M56" t="n">
+        <v>58.6789735483871</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3473,11 +3819,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LUTSIR PERSADA JAYA, PT</t>
+          <t>KHARISMA PERSADA, CV</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3485,17 +3831,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>60</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>paguyaman molombulahe</t>
+        </is>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K57" t="n">
+        <v>100</v>
+      </c>
       <c r="L57" t="n">
-        <v>65.16129032258064</v>
-      </c>
-      <c r="M57" t="inlineStr">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="M57" t="n">
+        <v>45.21818181818182</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3526,11 +3879,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1481</v>
+        <v>1443</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>CAHAYA AGUNG, CV</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3538,17 +3891,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>56.00000000000001</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>desa marisa selatan</t>
+        </is>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>100</v>
+      </c>
       <c r="L58" t="n">
-        <v>62.06896551724139</v>
-      </c>
-      <c r="M58" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="M58" t="n">
+        <v>42.8125</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3579,11 +3939,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1426</v>
+        <v>1482</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MULIA MULTI MANDIRI, CV</t>
+          <t>REKSO QUALITY UTAMA, PT</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3591,17 +3951,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>63.63636363636363</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>jl ratuwangi kabila poowo barat</t>
+        </is>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>33.3333</v>
+      </c>
+      <c r="K59" t="n">
+        <v>100</v>
+      </c>
       <c r="L59" t="n">
-        <v>69.45454545454545</v>
-      </c>
-      <c r="M59" t="inlineStr">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="M59" t="n">
+        <v>45.32162251461988</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3632,11 +3999,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2035</v>
+        <v>2148</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>POPA EYATO JAYA TAMA, PT</t>
+          <t>ANUGRAH JAYA PROPERTINDO, PT</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3644,19 +4011,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>46.42857142857143</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>jl jeruk no 56 dungingi huangobotu</t>
+        </is>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>33.3333</v>
       </c>
       <c r="K60" t="n">
-        <v>56.14035087719298</v>
+        <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>54.23417699177521</v>
-      </c>
-      <c r="M60" t="inlineStr">
+        <v>31.81818181818181</v>
+      </c>
+      <c r="M60" t="n">
+        <v>37.99760499108734</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3687,11 +4059,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1790</v>
+        <v>138</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>RIZKIA LESTARI, CV</t>
+          <t>SATYA HARDANA, CV</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3699,19 +4071,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>40</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>perum awara karya</t>
+        </is>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>75.86206896551724</v>
+        <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>68.76008804108584</v>
-      </c>
-      <c r="M61" t="inlineStr">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="M61" t="n">
+        <v>65</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3742,11 +4119,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>KARYA PATRIOT NUSANTARA, CV</t>
+          <t>YUNAN JAYA, CV</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3754,17 +4131,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>73.07692307692308</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>jl daud tayabu</t>
+        </is>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K62" t="n">
+        <v>100</v>
+      </c>
       <c r="L62" t="n">
-        <v>76.79045092838197</v>
-      </c>
-      <c r="M62" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="M62" t="n">
+        <v>44.41176470588236</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3795,11 +4179,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>292</v>
+        <v>247</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>INKA PRATAMA, CV</t>
+          <t>BERKAT YULANI, CV</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3807,17 +4191,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>76.47058823529412</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>botumoito potanga</t>
+        </is>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>100</v>
+      </c>
       <c r="L63" t="n">
-        <v>80.74866310160428</v>
-      </c>
-      <c r="M63" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M63" t="n">
+        <v>32.75862068965517</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3848,11 +4239,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1597</v>
+        <v>1672</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TIRTA TARUNA, CV</t>
+          <t>MOTIKACI FAMILY GROUP, CV</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3860,19 +4251,26 @@
           <t>7505</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>53.65853658536586</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>dsn pasar lama kwandang moluo</t>
+        </is>
       </c>
       <c r="J64" t="n">
         <v>100</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>100</v>
+      </c>
       <c r="L64" t="n">
-        <v>60.05046257359125</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>92.5925925925926</v>
+      </c>
+      <c r="M64" t="n">
+        <v>94.85094850948511</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -3901,11 +4299,11 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1481</v>
+        <v>1508</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>BINTANG KONSTRUKSI, CV</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3913,17 +4311,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>60.71428571428572</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>jl pasar minggu suwawa tengah alale</t>
+        </is>
       </c>
       <c r="J65" t="n">
-        <v>100</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K65" t="n">
+        <v>100</v>
+      </c>
       <c r="L65" t="n">
-        <v>65.20408163265307</v>
-      </c>
-      <c r="M65" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="M65" t="n">
+        <v>46.36734693877551</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -3966,19 +4371,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>100</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>jl kancil</t>
+        </is>
       </c>
       <c r="J66" t="n">
         <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>85.71428571428572</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
-        <v>94.47004608294931</v>
-      </c>
-      <c r="M66" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M66" t="n">
+        <v>100</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -4021,19 +4431,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>100</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>jl husin dj rahman</t>
+        </is>
       </c>
       <c r="J67" t="n">
         <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>92.30769230769231</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>95.63409563409563</v>
-      </c>
-      <c r="M67" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M67" t="n">
+        <v>100</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -4076,19 +4491,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>40</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>jl gelatik no.89 b</t>
+        </is>
       </c>
       <c r="J68" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>78.94736842105263</v>
+        <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>67.53911806543385</v>
-      </c>
-      <c r="M68" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M68" t="n">
+        <v>55</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4131,17 +4551,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>73.33333333333334</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>marisa marisa selatan</t>
+        </is>
       </c>
       <c r="J69" t="n">
-        <v>100</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K69" t="n">
+        <v>100</v>
+      </c>
       <c r="L69" t="n">
-        <v>78.41269841269842</v>
-      </c>
-      <c r="M69" t="inlineStr">
+        <v>48.27586206896552</v>
+      </c>
+      <c r="M69" t="n">
+        <v>55.44181034482759</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4172,11 +4599,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2215</v>
+        <v>1932</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MITRA JAYA MULTI SARANA, CV</t>
+          <t>UTAMA KARYA, CV</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4184,19 +4611,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>44.89795918367348</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>jl arief rahman hakim kota tengah dulalowo</t>
+        </is>
       </c>
       <c r="J70" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K70" t="n">
-        <v>92.6829268292683</v>
+        <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>71.3912394225983</v>
-      </c>
-      <c r="M70" t="inlineStr">
+        <v>22.22222222222223</v>
+      </c>
+      <c r="M70" t="n">
+        <v>63.16498316498316</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4227,11 +4659,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1347</v>
+        <v>1477</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JAYA MANDIRI PERSADA, CV</t>
+          <t>MANDIRI JAYA, CV</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4239,17 +4671,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>68.08510638297872</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>jl pasar minggu kabila dutohe</t>
+        </is>
       </c>
       <c r="J71" t="n">
-        <v>100</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="K71" t="n">
+        <v>100</v>
+      </c>
       <c r="L71" t="n">
-        <v>72.81323877068559</v>
-      </c>
-      <c r="M71" t="inlineStr">
+        <v>46.80851063829788</v>
+      </c>
+      <c r="M71" t="n">
+        <v>65.97678916827853</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4292,19 +4731,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>100</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>jl pelabuhan</t>
+        </is>
       </c>
       <c r="J72" t="n">
         <v>100</v>
       </c>
       <c r="K72" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L72" t="n">
-        <v>98.98039215686275</v>
-      </c>
-      <c r="M72" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M72" t="n">
+        <v>100</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -4335,11 +4779,11 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1419</v>
+        <v>101</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LOMAYA PUTRA, CV</t>
+          <t>EKA PUTRA, CV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4347,19 +4791,26 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>75.86206896551724</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>jl gagak, depan rm asta 6000</t>
+        </is>
       </c>
       <c r="J73" t="n">
         <v>100</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>100</v>
+      </c>
       <c r="L73" t="n">
-        <v>81.54158215010142</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M73" t="n">
+        <v>100</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4400,21 +4851,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>100</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>jl perum griya wiyan lestari d/1 kota tengah dulalowo</t>
+        </is>
       </c>
       <c r="J74" t="n">
         <v>100</v>
       </c>
       <c r="K74" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>72.41379310344827</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>77.14285714285714</v>
+      </c>
+      <c r="M74" t="n">
+        <v>83.52941176470588</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4443,11 +4899,11 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>265</v>
+        <v>26</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ARSA, CV</t>
+          <t>PUTERA BAHARI, CV</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4455,17 +4911,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>70.58823529411764</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>dsn tengah</t>
+        </is>
       </c>
       <c r="J75" t="n">
-        <v>100</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>100</v>
+      </c>
       <c r="L75" t="n">
-        <v>79.63800904977376</v>
-      </c>
-      <c r="M75" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>71.60493827160494</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4496,11 +4959,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>421</v>
+        <v>188</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>RAHMAT ABADI, CV</t>
+          <t>ANGLING DHARMA, CV</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4508,17 +4971,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>68.75</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>dsn tiga bulotu tilamuta ayuhulalo</t>
+        </is>
       </c>
       <c r="J76" t="n">
-        <v>100</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K76" t="n">
+        <v>100</v>
+      </c>
       <c r="L76" t="n">
-        <v>75</v>
-      </c>
-      <c r="M76" t="inlineStr">
+        <v>30.43478260869566</v>
+      </c>
+      <c r="M76" t="n">
+        <v>48.75776397515529</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4549,11 +5019,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1151</v>
+        <v>82</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GLORIA INDAH, CV</t>
+          <t>GOMINA PERMAI INDAH, CV</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4561,19 +5031,26 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>71.7948717948718</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>jl alwie abdul jalil habibie</t>
+        </is>
       </c>
       <c r="J77" t="n">
         <v>100</v>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>100</v>
+      </c>
       <c r="L77" t="n">
-        <v>75.97340930674264</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>30.76923076923077</v>
+      </c>
+      <c r="M77" t="n">
+        <v>73.80457380457381</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4591,40 +5068,29 @@
           <t>ALIF SATYA PERKASA, PT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>75nan</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>DESA TINELO</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>509</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>ALIF SETYA PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>95.45454545454545</v>
-      </c>
-      <c r="J78" t="n">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="K78" t="n">
-        <v>100</v>
-      </c>
-      <c r="L78" t="n">
-        <v>96.96969696969697</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>DROP</t>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4642,40 +5108,29 @@
           <t>ALIF SATYA PERKASA, PT</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>75nan</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>DESA TINELO</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>509</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>ALIF SETYA PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>95.45454545454545</v>
-      </c>
-      <c r="J79" t="n">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="K79" t="n">
-        <v>100</v>
-      </c>
-      <c r="L79" t="n">
-        <v>96.96969696969697</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>DROP</t>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4704,11 +5159,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SEMANGAT KARYA, CV</t>
+          <t>MULTI CAKRA, CV</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4716,17 +5171,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>63.41463414634146</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>tilamuta limbato</t>
+        </is>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
-      </c>
-      <c r="K80" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K80" t="n">
+        <v>100</v>
+      </c>
       <c r="L80" t="n">
-        <v>68.83468834688347</v>
-      </c>
-      <c r="M80" t="inlineStr">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="M80" t="n">
+        <v>42.48062015503876</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4757,11 +5219,11 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1434</v>
+        <v>1401</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SINAR LESTARI, CV</t>
+          <t>ANUGERAH ARAFAH LESTARI, PT</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4769,17 +5231,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>82.35294117647058</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>dutohe barat kabila dutohe barat</t>
+        </is>
       </c>
       <c r="J81" t="n">
-        <v>100</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K81" t="n">
+        <v>100</v>
+      </c>
       <c r="L81" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="M81" t="inlineStr">
+        <v>37.5</v>
+      </c>
+      <c r="M81" t="n">
+        <v>46.91666666666666</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4822,19 +5291,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>100</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>jl matolodula kota timur padebuolo</t>
+        </is>
       </c>
       <c r="J82" t="n">
         <v>100</v>
       </c>
       <c r="K82" t="n">
-        <v>89.65517241379311</v>
+        <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>95.40229885057471</v>
-      </c>
-      <c r="M82" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M82" t="n">
+        <v>100</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -4865,11 +5339,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1136</v>
+        <v>80</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>KURNIA LOGISTIK PRATAMA, PT</t>
+          <t>CILHAM EL ZAYYAN, CV</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4877,17 +5351,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>47.27272727272728</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>jl toto selatan</t>
+        </is>
       </c>
       <c r="J83" t="n">
-        <v>100</v>
-      </c>
-      <c r="K83" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>100</v>
+      </c>
       <c r="L83" t="n">
-        <v>53.86363636363637</v>
-      </c>
-      <c r="M83" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M83" t="n">
+        <v>40</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4918,11 +5399,11 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>246</v>
+        <v>5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SINAR ALINKO, CV</t>
+          <t>CAHAYA NUSA SULUTARINDO, PT</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4930,17 +5411,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>68.57142857142857</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>jl jendral sudirman nomor 35</t>
+        </is>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
-      </c>
-      <c r="K84" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>100</v>
+      </c>
       <c r="L84" t="n">
-        <v>74.03726708074534</v>
-      </c>
-      <c r="M84" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M84" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -4983,19 +5471,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>100</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>dsn muara</t>
+        </is>
       </c>
       <c r="J85" t="n">
         <v>100</v>
       </c>
       <c r="K85" t="n">
+        <v>100</v>
+      </c>
+      <c r="L85" t="n">
         <v>90</v>
       </c>
-      <c r="L85" t="n">
-        <v>96.20689655172414</v>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="M85" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -5026,11 +5519,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1392</v>
+        <v>1380</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CITRA ABDI KARYA, CV</t>
+          <t>JAYA ABADI, CV</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5038,17 +5531,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>65.21739130434783</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>suwawa bube</t>
+        </is>
       </c>
       <c r="J86" t="n">
-        <v>100</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K86" t="n">
+        <v>100</v>
+      </c>
       <c r="L86" t="n">
-        <v>69.85507246376811</v>
-      </c>
-      <c r="M86" t="inlineStr">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="M86" t="n">
+        <v>61.75215555555556</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5079,11 +5579,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>275</v>
+        <v>353</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CAHAYA AGRO KARYA, CV</t>
+          <t>ASRID JAYA, CV</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5091,17 +5591,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>64.86486486486487</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>jl trans sulawesi dsn taruna paguyaman tangkobu</t>
+        </is>
       </c>
       <c r="J87" t="n">
-        <v>100</v>
-      </c>
-      <c r="K87" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K87" t="n">
+        <v>100</v>
+      </c>
       <c r="L87" t="n">
-        <v>71.8918918918919</v>
-      </c>
-      <c r="M87" t="inlineStr">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="M87" t="n">
+        <v>53.87755102040817</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5144,21 +5651,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>100</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>jl padang e no 3 sipatana tapa</t>
+        </is>
       </c>
       <c r="J88" t="n">
         <v>100</v>
       </c>
       <c r="K88" t="n">
-        <v>50.84745762711864</v>
+        <v>100</v>
       </c>
       <c r="L88" t="n">
-        <v>67.48370273794004</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>54.90196078431372</v>
+      </c>
+      <c r="M88" t="n">
+        <v>72.17355027117229</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -5187,11 +5699,11 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1442</v>
+        <v>100</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NUSA INDAH, CV</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5199,17 +5711,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>77.41935483870968</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>jl pelabuhan</t>
+        </is>
       </c>
       <c r="J89" t="n">
-        <v>100</v>
-      </c>
-      <c r="K89" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>100</v>
+      </c>
       <c r="L89" t="n">
-        <v>81.72043010752688</v>
-      </c>
-      <c r="M89" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M89" t="n">
+        <v>60.60606060606061</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5252,19 +5771,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>100</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>jl cut nyak dien kota timur heledulaa</t>
+        </is>
       </c>
       <c r="J90" t="n">
         <v>100</v>
       </c>
       <c r="K90" t="n">
-        <v>91.42857142857143</v>
+        <v>100</v>
       </c>
       <c r="L90" t="n">
-        <v>96.74285714285713</v>
-      </c>
-      <c r="M90" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M90" t="n">
+        <v>100</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -5295,11 +5819,11 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SINAR PURNAMA, CV</t>
+          <t>SINAR PRATAMA BOALEMO, PT</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5307,17 +5831,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>75</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>jl raja palowa no 29 tilamuta hungayonaa</t>
+        </is>
       </c>
       <c r="J91" t="n">
-        <v>100</v>
-      </c>
-      <c r="K91" t="inlineStr"/>
+        <v>66.66670000000001</v>
+      </c>
+      <c r="K91" t="n">
+        <v>100</v>
+      </c>
       <c r="L91" t="n">
-        <v>78.70370370370371</v>
-      </c>
-      <c r="M91" t="inlineStr">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="M91" t="n">
+        <v>64.26810105820105</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5348,11 +5879,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1139</v>
+        <v>69</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CITOS, CV</t>
+          <t>SRI RAHMAT AGUNG, CV</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5360,17 +5891,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>60</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>duhiadaa duhiadaa</t>
+        </is>
       </c>
       <c r="J92" t="n">
-        <v>100</v>
-      </c>
-      <c r="K92" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>100</v>
+      </c>
       <c r="L92" t="n">
-        <v>70.66666666666667</v>
-      </c>
-      <c r="M92" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5413,19 +5951,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>87.17948717948718</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>jl imam bonjol dsn ii ds. piloliyanga tilamuta piloliyanga</t>
+        </is>
       </c>
       <c r="J93" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K93" t="n">
-        <v>27.45098039215686</v>
+        <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>67.55656108597285</v>
-      </c>
-      <c r="M93" t="inlineStr">
+        <v>33.9622641509434</v>
+      </c>
+      <c r="M93" t="n">
+        <v>64.31865828092243</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5456,11 +5999,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INDAH KERAMIK, CV</t>
+          <t>SURYA INDAH, CV</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5468,17 +6011,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>72.72727272727273</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>jl sudirman tilamuta limbato</t>
+        </is>
       </c>
       <c r="J94" t="n">
-        <v>100</v>
-      </c>
-      <c r="K94" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K94" t="n">
+        <v>100</v>
+      </c>
       <c r="L94" t="n">
-        <v>78.18181818181819</v>
-      </c>
-      <c r="M94" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="M94" t="n">
+        <v>63.27272727272727</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5509,11 +6059,11 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>RIDWAN, CV</t>
+          <t>NURUL JANNAH, CV</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5521,17 +6071,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>56.00000000000001</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>jl budi makmur dsn 2 bulango selatan lamahu</t>
+        </is>
       </c>
       <c r="J95" t="n">
-        <v>100</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K95" t="n">
+        <v>100</v>
+      </c>
       <c r="L95" t="n">
-        <v>65.26315789473684</v>
-      </c>
-      <c r="M95" t="inlineStr">
+        <v>36.73469387755102</v>
+      </c>
+      <c r="M95" t="n">
+        <v>52.08006279434851</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5562,11 +6119,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1160</v>
+        <v>80</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>JDS RAYA, CV</t>
+          <t>CILHAM EL ZAYYAN, CV</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5574,17 +6131,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>57.14285714285714</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>jl toto selatan</t>
+        </is>
       </c>
       <c r="J96" t="n">
-        <v>100</v>
-      </c>
-      <c r="K96" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>100</v>
+      </c>
       <c r="L96" t="n">
-        <v>70.32967032967032</v>
-      </c>
-      <c r="M96" t="inlineStr">
+        <v>68.75</v>
+      </c>
+      <c r="M96" t="n">
+        <v>61.20689655172414</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5627,19 +6191,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>100</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>perum belle orasawa, jl palma dungingi libuo</t>
+        </is>
       </c>
       <c r="J97" t="n">
         <v>100</v>
       </c>
       <c r="K97" t="n">
-        <v>44.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="L97" t="n">
-        <v>84.875</v>
-      </c>
-      <c r="M97" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M97" t="n">
+        <v>100</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -5670,11 +6239,11 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CAHAYA AGUNG, CV</t>
+          <t>CAHAYA IDAMAN, CV</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5682,17 +6251,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>81.25</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>dsn i tilamuta modelomo</t>
+        </is>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
-      </c>
-      <c r="K98" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K98" t="n">
+        <v>100</v>
+      </c>
       <c r="L98" t="n">
-        <v>85</v>
-      </c>
-      <c r="M98" t="inlineStr">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="M98" t="n">
+        <v>55.30612244897959</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5735,19 +6311,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>100</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>jl sultan hasanudin kota selatan biawao</t>
+        </is>
       </c>
       <c r="J99" t="n">
         <v>100</v>
       </c>
       <c r="K99" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L99" t="n">
-        <v>97.23684210526316</v>
-      </c>
-      <c r="M99" t="inlineStr">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="M99" t="n">
+        <v>81.1111111111111</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -5790,19 +6371,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>100</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>jl beringin kelurahan tomulobutao selatan dungingi tomulabutao selatan</t>
+        </is>
       </c>
       <c r="J100" t="n">
         <v>100</v>
       </c>
       <c r="K100" t="n">
-        <v>50.90909090909091</v>
+        <v>100</v>
       </c>
       <c r="L100" t="n">
-        <v>83.63636363636364</v>
-      </c>
-      <c r="M100" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M100" t="n">
+        <v>100</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -5833,11 +6419,11 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1208</v>
+        <v>1043</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SPEKTEK, CV</t>
+          <t>BINTANG ANTARIKSA NUSANTARA RAYA, PT</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5845,17 +6431,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>66.66666666666667</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>marisa marisa utara</t>
+        </is>
       </c>
       <c r="J101" t="n">
-        <v>100</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
       <c r="L101" t="n">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="M101" t="inlineStr">
+        <v>58.8235294117647</v>
+      </c>
+      <c r="M101" t="n">
+        <v>55.46218487394957</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5886,11 +6479,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1404</v>
+        <v>100</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BRESCIA SEJAHTERA SELATAN, PT</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5898,17 +6491,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>62.5</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>jl pelabuhan</t>
+        </is>
       </c>
       <c r="J102" t="n">
-        <v>100</v>
-      </c>
-      <c r="K102" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>100</v>
+      </c>
       <c r="L102" t="n">
-        <v>69.02173913043478</v>
-      </c>
-      <c r="M102" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M102" t="n">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5939,11 +6539,11 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>364</v>
+        <v>25</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
+          <t>HADFIR PERKASA, CV</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5951,17 +6551,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>78.26086956521739</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>perum padengo permai 6 blok c nomor 1</t>
+        </is>
       </c>
       <c r="J103" t="n">
-        <v>100</v>
-      </c>
-      <c r="K103" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>100</v>
+      </c>
       <c r="L103" t="n">
-        <v>84.47204968944099</v>
-      </c>
-      <c r="M103" t="inlineStr">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="M103" t="n">
+        <v>68.2170542635659</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -5992,11 +6599,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ANUGERAH ABADI, CV</t>
+          <t>MEDIA BINTANG UTAMA, CV</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6004,17 +6611,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>61.11111111111111</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>tilamuta limbato</t>
+        </is>
       </c>
       <c r="J104" t="n">
-        <v>100</v>
-      </c>
-      <c r="K104" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="K104" t="n">
+        <v>100</v>
+      </c>
       <c r="L104" t="n">
-        <v>68.18181818181819</v>
-      </c>
-      <c r="M104" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="M104" t="n">
+        <v>51.55555555555556</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6045,11 +6659,11 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>844</v>
+        <v>902</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DWI AULIA PERKASA, CV</t>
+          <t>REZA STAR, CV</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6057,17 +6671,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>71.7948717948718</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>dsn 1 tilango tenggela</t>
+        </is>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>100</v>
+      </c>
       <c r="L105" t="n">
-        <v>76.92307692307692</v>
-      </c>
-      <c r="M105" t="inlineStr">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="M105" t="n">
+        <v>69.53405017921148</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6098,11 +6719,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1906</v>
+        <v>126</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LIMA SATU, CV</t>
+          <t>TULUS MULIA, CV</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6110,19 +6731,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>64.28571428571428</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>jl gunung boliohuto</t>
+        </is>
       </c>
       <c r="J106" t="n">
         <v>100</v>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>100</v>
+      </c>
       <c r="L106" t="n">
-        <v>71.80451127819549</v>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M106" t="n">
+        <v>100</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6151,11 +6779,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1408</v>
+        <v>96</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIRAHMATI, CV</t>
+          <t>DWI SAMA, CV</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6163,19 +6791,26 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>72</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>jalan taman buah desa talango kabila talango</t>
+        </is>
       </c>
       <c r="J107" t="n">
         <v>100</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>100</v>
+      </c>
       <c r="L107" t="n">
-        <v>79</v>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M107" t="n">
+        <v>100</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6216,21 +6851,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>100</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>jl palma nomor 16</t>
+        </is>
       </c>
       <c r="J108" t="n">
         <v>100</v>
       </c>
       <c r="K108" t="n">
-        <v>42.30769230769231</v>
+        <v>100</v>
       </c>
       <c r="L108" t="n">
-        <v>66.89785624211854</v>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>38.46153846153846</v>
+      </c>
+      <c r="M108" t="n">
+        <v>69.9463327370304</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6271,17 +6911,24 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>100</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>kabila oluhuta</t>
+        </is>
       </c>
       <c r="J109" t="n">
         <v>100</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>100</v>
+      </c>
       <c r="L109" t="n">
         <v>100</v>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="M109" t="n">
+        <v>100</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -6312,11 +6959,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1955</v>
+        <v>136</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ADI CIPTA UTAMAI, CV</t>
+          <t>BINTANG PALMA, CV</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6324,21 +6971,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>59.45945945945945</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>jl palma, no 154.</t>
+        </is>
       </c>
       <c r="J110" t="n">
         <v>100</v>
       </c>
       <c r="K110" t="n">
-        <v>55.67010309278351</v>
+        <v>100</v>
       </c>
       <c r="L110" t="n">
-        <v>59.12351231938861</v>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M110" t="n">
+        <v>100</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6367,11 +7019,11 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1955</v>
+        <v>2078</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ADI CIPTA UTAMAI, CV</t>
+          <t>CAHAYA TOFANI, CV</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6379,19 +7031,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>50</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>jl moh. yamin ii kota selatan limba u dua</t>
+        </is>
       </c>
       <c r="J111" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K111" t="n">
-        <v>68.08510638297872</v>
+        <v>100</v>
       </c>
       <c r="L111" t="n">
-        <v>63.94479585968948</v>
-      </c>
-      <c r="M111" t="inlineStr">
+        <v>56.25</v>
+      </c>
+      <c r="M111" t="n">
+        <v>53.57142857142857</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6422,11 +7079,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>TITIAN PRATAMA, CV</t>
+          <t>RIZKY ADITYA PRATAMA, CV</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6434,19 +7091,26 @@
           <t>7504</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>61.90476190476191</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>jl muhclis rahim botu pingge tanah putih</t>
+        </is>
       </c>
       <c r="J112" t="n">
         <v>100</v>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>100</v>
+      </c>
       <c r="L112" t="n">
-        <v>67.34693877551021</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>74.57627118644068</v>
+      </c>
+      <c r="M112" t="n">
+        <v>87.84082535003685</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6475,11 +7139,11 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ARYA PRATAMA, CV</t>
+          <t>ARITO PRATAMA, CV</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6487,19 +7151,26 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>84.84848484848484</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>dsn duhi paguyaman molombulahe</t>
+        </is>
       </c>
       <c r="J113" t="n">
         <v>100</v>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>100</v>
+      </c>
       <c r="L113" t="n">
-        <v>87.73448773448773</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>82.35294117647058</v>
+      </c>
+      <c r="M113" t="n">
+        <v>88.01331853496114</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6528,11 +7199,11 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BERKAH ANUGRAH, CV</t>
+          <t>ANUGERAH PRATAMA, PT</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6540,17 +7211,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>78.94736842105263</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>tilango tinelo</t>
+        </is>
       </c>
       <c r="J114" t="n">
-        <v>100</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K114" t="n">
+        <v>100</v>
+      </c>
       <c r="L114" t="n">
-        <v>82.45614035087719</v>
-      </c>
-      <c r="M114" t="inlineStr">
+        <v>37.03703703703704</v>
+      </c>
+      <c r="M114" t="n">
+        <v>50.95398428731762</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6593,19 +7271,24 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>100</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>jl jambura</t>
+        </is>
       </c>
       <c r="J115" t="n">
         <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>90.90909090909091</v>
+        <v>100</v>
       </c>
       <c r="L115" t="n">
-        <v>95.63636363636364</v>
-      </c>
-      <c r="M115" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M115" t="n">
+        <v>100</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -6648,17 +7331,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>100</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>tilamuta limbato</t>
+        </is>
       </c>
       <c r="J116" t="n">
         <v>100</v>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>100</v>
+      </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="M116" t="n">
+        <v>100</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -6689,11 +7379,11 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>BAROKAH ABADI, CV</t>
+          <t>BOALEMO LAHIDIYA, CV</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6701,17 +7391,24 @@
           <t>7501</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>62.06896551724138</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>tilamuta limbato</t>
+        </is>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>100</v>
+      </c>
       <c r="L117" t="n">
-        <v>71.55172413793103</v>
-      </c>
-      <c r="M117" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M117" t="n">
+        <v>80</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6754,21 +7451,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>100</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>perum awara karya</t>
+        </is>
       </c>
       <c r="J118" t="n">
         <v>100</v>
       </c>
       <c r="K118" t="n">
-        <v>53.84615384615385</v>
+        <v>100</v>
       </c>
       <c r="L118" t="n">
-        <v>71.15384615384616</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>78.57142857142857</v>
+      </c>
+      <c r="M118" t="n">
+        <v>87.24489795918367</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6797,11 +7499,11 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1933</v>
+        <v>158</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DAR AL TAUHID, CV</t>
+          <t>RARA BERKAH, CV</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6809,19 +7511,26 @@
           <t>7571</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>50</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>jl kancil</t>
+        </is>
       </c>
       <c r="J119" t="n">
         <v>100</v>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>100</v>
+      </c>
       <c r="L119" t="n">
-        <v>60.52631578947368</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>INSERT</t>
+        <v>100</v>
+      </c>
+      <c r="M119" t="n">
+        <v>100</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6850,11 +7559,11 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>758</v>
+        <v>561</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ADHITYA, CV</t>
+          <t>ARUL JAYA, PT</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6862,17 +7571,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>58.06451612903225</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>jl brijen piola isa limboto hunggaluwa</t>
+        </is>
       </c>
       <c r="J120" t="n">
-        <v>100</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>100</v>
+      </c>
       <c r="L120" t="n">
-        <v>65.05376344086021</v>
-      </c>
-      <c r="M120" t="inlineStr">
+        <v>61.33333333333334</v>
+      </c>
+      <c r="M120" t="n">
+        <v>47.55555555555556</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>INSERT</t>
         </is>
@@ -6915,17 +7631,24 @@
           <t>7503</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>100</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>buntulia buntulia tengah</t>
+        </is>
       </c>
       <c r="J121" t="n">
         <v>100</v>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>100</v>
+      </c>
       <c r="L121" t="n">
-        <v>100</v>
-      </c>
-      <c r="M121" t="inlineStr">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="M121" t="n">
+        <v>82.09718670076725</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -6968,19 +7691,24 @@
           <t>7502</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>100</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>perum asabri blok e nomor 3 telaga biru ulapato.a</t>
+        </is>
       </c>
       <c r="J122" t="n">
         <v>100</v>
       </c>
       <c r="K122" t="n">
-        <v>77.41935483870968</v>
+        <v>100</v>
       </c>
       <c r="L122" t="n">
-        <v>86.13469156762875</v>
-      </c>
-      <c r="M122" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="M122" t="n">
+        <v>100</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>

--- a/monitoring_weighted_similarity.xlsx
+++ b/monitoring_weighted_similarity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,10 +497,8 @@
           <t>SINAR LUPOYO LESTARI, CV</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+      <c r="D2" t="n">
+        <v>7501</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -508,27 +506,29 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>1242</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SINAR SARI, CV</t>
+          <t>PANUA LESTARI, CV</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>73.68421052631579</v>
+        <v>73.17073170731707</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.4814814814815</v>
+      </c>
       <c r="L2" t="n">
-        <v>77.4436090225564</v>
+        <v>66.51741879737638</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -550,10 +550,8 @@
           <t>FITRA PERSADA MANDIRI, CV</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+      <c r="D3" t="n">
+        <v>7571</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -577,13 +575,13 @@
         <v>62.22222222222222</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>92.30769230769231</v>
       </c>
       <c r="L3" t="n">
-        <v>77.88034188034187</v>
+        <v>67.19263642340565</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -602,43 +600,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MEGA ARTERI, CV</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>DUA PUTRA SANJAYA, CV</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7501</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jalan Palma Nomor 49</t>
+          <t>JALAN SIWA 2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2217</v>
+        <v>1028</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEGA ARTERI, CV</t>
+          <t>DUA PUTRA SANJAYA, CV</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>57.14285714285714</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="L4" t="n">
-        <v>78.02197802197801</v>
+        <v>65.24216524216524</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -657,43 +653,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PURIMA JAYA SEJAHTERA, CV</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>MOHUYULA JAYA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Taman Sari</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2074</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIMUR JAYA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Jalan Prof. Dr. H. Hasan Abas.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2126</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>USAHA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>52.38095238095239</v>
+        <v>83.01886792452831</v>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>71.69811320754718</v>
+        <v>26.08695652173914</v>
       </c>
       <c r="L5" t="n">
-        <v>65.43164755508856</v>
+        <v>58.759042434186</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -712,47 +706,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FARAZ JAYA ABADI, CV</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>TANDAN PRIMA SENTOSA, CV</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7504</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jalan Tinaloga</t>
+          <t>DUSUN ABADI</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2133</v>
+        <v>872</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FARAZ JAYA ABADI, CV</t>
+          <t>PURNA PRASETYA, CV</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
-      </c>
-      <c r="K6" t="n">
-        <v>88</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>95.57894736842105</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -767,41 +757,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DWINANTA PUTRA PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>JASA BARU, CV</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7571</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jalan Rahmat Baru</t>
+          <t>Jalan Palma</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1191</v>
+        <v>1824</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PUTRA MITRA PERKASA, CV</t>
+          <t>KARYA BERSAMA, CV</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>73.46938775510203</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.21052631578947</v>
+      </c>
       <c r="L7" t="n">
-        <v>77.00680272108842</v>
+        <v>56.87719298245614</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -820,47 +810,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEDAYU BERKAT KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>AZWA UTAMA, PT</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jl. Rambutan No. 33</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1693</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LINGGA PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Jalan Raden Saleh</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2155</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SEDAYU BERKAT KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>90.32258064516128</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="L8" t="n">
-        <v>96.6425279789335</v>
+        <v>53.67521367521368</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -875,43 +863,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONG TIMUR, CV</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>IRGI ELEKTRIKAL, PT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7501</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JALAN RAJAWALI</t>
+          <t>JL. SIMON P.H LIPOETO</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2199</v>
+        <v>557</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORONG TIMUR, CV</t>
+          <t>ARUL JAYA ELEKTRIK, PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="J9" t="n">
-        <v>100</v>
-      </c>
-      <c r="K9" t="n">
-        <v>46.15384615384615</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>77.82805429864254</v>
+        <v>48.19512195121951</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -930,41 +914,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YUMAN RAYA, CV</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>AGUNG RAYA, CV</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7571</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelurahan Tenilo</t>
+          <t>Jalan Cendrawasih Nomor 57</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>1072</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KUMALA JAYA, CV</t>
+          <t>AGUNG UTAMA, CV</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>75.86206896551724</v>
+        <v>82.75862068965517</v>
       </c>
       <c r="J10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>81.22605363984674</v>
+        <v>57.93103448275863</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -983,41 +965,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TEKNIK JASA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>PENCAKAR LANGIT, CV</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7505</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Desa Mongolato,Kecamatan Telaga,Kabupaten Gorontalo</t>
+          <t>Desa Molingkapoto</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>406</v>
+        <v>1657</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FAJAR MANDIRI, CV</t>
+          <t>PENCAKAR LANGIT, CV</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>94.11764705882352</v>
+      </c>
       <c r="L11" t="n">
-        <v>74.44444444444444</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1036,47 +1018,43 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RIFKA MUTIARA INDAH, PT</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>TRI NURFI PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7501</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dusun II</t>
+          <t>Dusun Bontula</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RIFKA MUTIARA INDAH, PT</t>
+          <t>TRI NURFI PRATAMA, CV</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
-      </c>
-      <c r="K12" t="n">
-        <v>85.71428571428572</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>96.73469387755102</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -1091,41 +1069,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PUTRA GOSAM, CV</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>NUR MAHABBAH, CV</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7502</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dulupi</t>
+          <t>JALAN YOS SUDARSO</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>661</v>
+        <v>506</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PUTRA POSEIDON, CV</t>
+          <t>NUR MAHABBAH, CV</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>72.72727272727273</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>78.57142857142857</v>
+      </c>
       <c r="L13" t="n">
-        <v>78.4688995215311</v>
+        <v>75.27472527472527</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1144,41 +1122,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ABADI JAYA KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>TOEKANG KELOE, CV</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7505</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Desa Patoameme</t>
+          <t>JALAN TRANS SULAWESI</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>776</v>
+        <v>1655</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HAYUTAMA KONSTRUKSINDO, CV</t>
+          <t>TOEKANG KELOE, CV</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>70.58823529411764</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>91.89189189189189</v>
+      </c>
       <c r="L14" t="n">
-        <v>74.64503042596348</v>
+        <v>82.27529855436832</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1197,41 +1175,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NUSANTARA BOALEMO, CV</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>MULTAZAM, CV</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7501</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dusun I</t>
+          <t>DUSUN I , DESA BUNGGALO</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>973</v>
+        <v>1413</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BINTANG NUSANTARA, CV</t>
+          <t>GUNUNG TILONGKABILA, CV</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>71.42857142857143</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66.66666666666667</v>
+      </c>
       <c r="L15" t="n">
-        <v>76</v>
+        <v>50.77816492450639</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1250,41 +1228,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MEGALODON CIPTA KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>BINTANG GANI PRATAMA, PT</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7501</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DESA TOTO UTARA</t>
+          <t>Lingkungan I</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1141</v>
+        <v>824</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CITRA NUSANTARA, CV</t>
+          <t>ANUGERAH PRATAMA, PT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>53.06122448979591</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="J16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>58.58343337334934</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1303,43 +1279,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RADESTA KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SIHIDANGORI, CV</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7503</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dusun IV</t>
+          <t>Jalan Muchlis Rahim</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>455</v>
+        <v>75</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MALIKA KONSTRUKSI, CV</t>
+          <t>SIHIDANGORI, CV</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>79.06976744186046</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>22.72727272727273</v>
+        <v>91.42857142857143</v>
       </c>
       <c r="L17" t="n">
-        <v>68.27509016291506</v>
+        <v>80.92857142857142</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1358,43 +1332,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALEXA STAR, CV</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>ALSYA MANDIRI KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7501</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jl. Trans Sulawesi</t>
+          <t>Desa Pentadio Timur</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>1118</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BERKAH ANNUR MARISA, PT</t>
+          <t>ALIAYAH MANDIRI, CV</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>37.83783783783784</v>
+        <v>63.82978723404256</v>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K18" t="n">
-        <v>97.14285714285714</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>74.3972543972544</v>
+        <v>52.5657071339174</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1413,41 +1383,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARITO PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>NUANSA MANDIRI UTAMA, CV</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7502</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Jalan Karim Mahmud</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>52</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NUANSA MANDIRI UTAMA, CV</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>7502</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Dusun Gompase Induk</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>984</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ARIES PRATAMA TEKNIK, CV</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>73.17073170731707</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>90.90909090909091</v>
+      </c>
       <c r="L19" t="n">
-        <v>78.28106852497096</v>
+        <v>84.09090909090908</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1466,43 +1436,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ANSIR JAYA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
+          <t>ALDHIRA JAYA ABADI, CV</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7503</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Desa Moluo</t>
+          <t>JALAN THAYEB MOHAMAD GOBEL, DESA TINELO AYULA, KECAMATAN BULANGO SELATAN, KABUPATEN BONE BOLANGO, PROVINSI GORONTALO.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1609</v>
+        <v>1380</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ASYROF JAYA MANDIRI, CV</t>
+          <t>JAYA ABADI, CV</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="J20" t="n">
-        <v>100</v>
-      </c>
-      <c r="K20" t="n">
-        <v>38.09523809523809</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>76.01410934744268</v>
+        <v>61.11111111111112</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1521,47 +1487,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FANTASTIC ENGINEER, CV</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SHINDY BAROKAH, CV</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7505</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dusun I Mekar Sari</t>
+          <t>Dusun Mangrove</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FANTASTIC ENGINEER, CV</t>
+          <t>SHINDY BAROKAH, CV</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>94.11764705882352</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="L21" t="n">
-        <v>97.59358288770053</v>
+        <v>81.37651821862349</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -1576,41 +1540,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAGITA CAHAYA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>AMANAHMU, CV</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7504</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PERUM GRIYA MARISA INDAH, BLOK M, NOMOR 2</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1286</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AMALIA, CV</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>7503</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>DESA TIMBUOLO</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1229</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CAHAYA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>83.72093023255813</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>62.65060240963856</v>
+      </c>
       <c r="L22" t="n">
-        <v>85.96631916599839</v>
+        <v>58.32884697495685</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1629,43 +1593,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INDAH JAYA KARYA POHUWATO, PT</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>CANANG SARI SEJAHTERA, CV</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7502</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>jalan Pelabuhan</t>
+          <t>Desa Bongo III</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>485</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
+          <t>ABADI SEJAHTERA, CV</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>60.31746031746032</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
-      </c>
-      <c r="K23" t="n">
-        <v>88.88888888888889</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>72.55291005291006</v>
+        <v>58.65102639296188</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1684,43 +1644,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DUA TUJUH SEDARAH, PT</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>MITRA NUSANTARA INDONESIA, CV</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7501</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jl. Kancil</t>
+          <t>JL. MARIDU HAYA NO.264A</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2082</v>
+        <v>1263</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TUJUH DUA JAYA, CV</t>
+          <t>SINAR PERMATA INDAH, CV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>66.66666666666667</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
-      </c>
-      <c r="K24" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>65.71428571428571</v>
+        <v>54.17582417582418</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1739,43 +1695,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PROSES GROUP, CV</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>MEGA ARTERI, CV</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Jalan Palma Nomor 49</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2217</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MEGA ARTERI, CV</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Jalan Bandes, Kelurahan Bulotadaa Timur, Kecamatan Sipatana</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1803</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>GALANG PERDANA, CV</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>41.17647058823529</v>
+        <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>50.52631578947368</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="L25" t="n">
-        <v>51.13767292393307</v>
+        <v>64.45993031358884</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1794,43 +1748,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TRISANDI LAGUNA, CV</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>PURIMA JAYA SEJAHTERA, CV</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7571</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jalan Bali Perum Hafair Mas Blok B</t>
+          <t>Jalan Prof. Dr. H. Hasan Abas.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2245</v>
+        <v>1193</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DALIA PERSADA, CV</t>
+          <t>RINDANG SEJAHTERA, CV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>55.55555555555556</v>
+        <v>73.91304347826086</v>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K26" t="n">
-        <v>59.15492957746478</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>60.82145896823436</v>
+        <v>59.60729312762972</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1849,41 +1799,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZAHRA GEMILANG, CV</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>LAKARA BUANA INDAH, CV</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dusun 2, Desa Pentadio Barat, Kab Gorontalo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MARKA INDAH, CV</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DUSUN II</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>305</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MIWAN STAR, CV</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>62.5</v>
+        <v>70.27027027027026</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>69.31818181818181</v>
+        <v>55.21235521235521</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1902,41 +1850,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DUA PUTRA SANJAYA, CV</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>MANDIRI DUA, CV</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Jl. Musa Kaluku</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>470</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DUTA MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>JALAN SIWA 2</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>281</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DUA PUTRA, CV</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>76.47058823529412</v>
+        <v>90.32258064516128</v>
       </c>
       <c r="J28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>80.23529411764706</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1955,41 +1901,39 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MOHUYULA JAYA KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>ARTHA DENANTARA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7571</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Taman Sari</t>
+          <t>Jalan Dr. Umar Sidiki, Kel. Wonggaditi, Kec. Kota Utara, Kota Gorontalo, Provinsi Gorontalo</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1187</v>
+        <v>776</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PRIMA JAYA, CV</t>
+          <t>HAYUTAMA KONSTRUKSINDO, CV</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>57.14285714285714</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>62.5</v>
+        <v>56.54761904761905</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2008,41 +1952,39 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TANDAN PRIMA SENTOSA, CV</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>ARMI PRATAMA JAYA, PT</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7503</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DUSUN ABADI</t>
+          <t>Desa Tanggilingo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1488</v>
+        <v>574</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SINAR PERMATA, CV</t>
+          <t>CITRA ADIJAYA PRATAMA, PT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>63.41463414634146</v>
+        <v>73.91304347826086</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>68.6411149825784</v>
+        <v>57.487922705314</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2061,43 +2003,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JASA BARU, CV</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>FARAZ JAYA ABADI, CV</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Jalan Tinaloga</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2133</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>FARAZ JAYA ABADI, CV</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Jalan Palma</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1824</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>KARYA BERSAMA, CV</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>84.21052631578947</v>
+        <v>88</v>
       </c>
       <c r="L31" t="n">
-        <v>75.22556390977444</v>
+        <v>80.8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2116,43 +2056,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AZWA UTAMA, PT</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>DWINANTA PUTRA PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7503</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jl. Rambutan No. 33</t>
+          <t>Jalan Rahmat Baru</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1693</v>
+        <v>1470</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LINGGA PRATAMA, CV</t>
+          <t>DWINANTA PUTRA PRATAMA, CV</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>73.33333333333334</v>
+        <v>90.32258064516128</v>
       </c>
       <c r="L32" t="n">
-        <v>67.38738738738739</v>
+        <v>84.39763001974983</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2171,41 +2109,41 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IRGI ELEKTRIKAL, PT</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SEDAYU BERKAT KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7571</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JL. SIMON P.H LIPOETO</t>
+          <t>Jalan Raden Saleh</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>2155</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RITNI LESTARI, CV</t>
+          <t>SEDAYU BERKAT KONSTRUKSI, CV</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>55.55555555555556</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>90.32258064516128</v>
+      </c>
       <c r="L33" t="n">
-        <v>63.28502415458938</v>
+        <v>85.00948766603415</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2224,43 +2162,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AGUNG RAYA, CV</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>CORONG TIMUR, CV</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JALAN RAJAWALI</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CORONG TIMUR, CV</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Jalan Cendrawasih Nomor 57</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1735</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>BRAWIJAYA SAKTI, CV</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>42.42424242424242</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>70</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="L34" t="n">
-        <v>63.95316804407714</v>
+        <v>62.39316239316239</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2279,47 +2215,45 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PENCAKAR LANGIT, CV</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
+          <t>YUMAN RAYA, CV</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7501</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Desa Molingkapoto</t>
+          <t>Kelurahan Tenilo</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1657</v>
+        <v>757</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PENCAKAR LANGIT, CV</t>
+          <t>SINAR KOTA, CV</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>94.11764705882352</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>97.5</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -2334,41 +2268,39 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TRI NURFI PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>TEKNIK JASA MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Desa Mongolato,Kecamatan Telaga,Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>406</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>FAJAR MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Dusun Bontula</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>337</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>TEGAR GITA PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>74.41860465116279</v>
+        <v>70</v>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>78.51162790697674</v>
+        <v>55.51724137931034</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2387,41 +2319,41 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NUR MAHABBAH, CV</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>RIFKA MUTIARA INDAH, PT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7501</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>JALAN YOS SUDARSO</t>
+          <t>Dusun II</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>925</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>YENTRI JAYA, CV</t>
+          <t>RIFKA MUTIARA INDAH, PT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>58.06451612903225</v>
+        <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>85.71428571428572</v>
+      </c>
       <c r="L37" t="n">
-        <v>66.45161290322581</v>
+        <v>80.6949806949807</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2440,47 +2372,43 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TOEKANG KELOE, CV</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
+          <t>PUTRA GOSAM, CV</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7502</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JALAN TRANS SULAWESI</t>
+          <t>Dulupi</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1655</v>
+        <v>477</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TOEKANG KELOE, CV</t>
+          <t>PUTRA GOSAM, CV</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
-      </c>
-      <c r="K38" t="n">
-        <v>91.89189189189189</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>96.04482531311798</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -2495,41 +2423,41 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MULTAZAM, CV</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SEXY ROAD INDO, CV</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7571</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DUSUN I , DESA BUNGGALO</t>
+          <t>Perum Asabri Blok E/03</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>360</v>
+        <v>55</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUFNAZ, CV</t>
+          <t>SEXY ROAD INDO, CV</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>72.72727272727273</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>77.55102040816327</v>
+      </c>
       <c r="L39" t="n">
-        <v>79.54545454545455</v>
+        <v>76.22005323868677</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2548,41 +2476,41 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BINTANG GANI PRATAMA, PT</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>GAMMA RAYA, CV</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7571</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lingkungan I</t>
+          <t>Jalan Rusli Datau 1 Perumahan Alya III Blok B Nomor 2</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BINA PRATAMA, CV</t>
+          <t>GAMMA RAYA, CV</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>92.92929292929293</v>
+      </c>
       <c r="L40" t="n">
-        <v>74.28571428571429</v>
+        <v>86.64729486647295</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2601,47 +2529,45 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SIHIDANGORI, CV</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>TRI BAROKAH PERKASA, PT</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7503</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jalan Muchlis Rahim</t>
+          <t>Jl. Kasmat Lahay</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SIHIDANGORI, CV</t>
+          <t>TRI PUTRA PERKASA, CV</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>91.42857142857143</v>
+        <v>51.85185185185186</v>
       </c>
       <c r="L41" t="n">
-        <v>95.71428571428571</v>
+        <v>55.60793116348673</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -2656,41 +2582,41 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ALSYA MANDIRI KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>INDO KONSTRUKSI PERSADA, PT</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7501</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Desa Pentadio Timur</t>
+          <t>Jalan Sun Ismail Perum Latoro</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>486</v>
+        <v>1020</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AAVAIRO MANDIRI JAYA, CV</t>
+          <t>INDO KONSTRUKSI PERSADA, PT</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>57.69230769230769</v>
+        <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>100</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>94.54545454545455</v>
+      </c>
       <c r="L42" t="n">
-        <v>62.98076923076923</v>
+        <v>87.77126099706746</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2709,47 +2635,43 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NUANSA MANDIRI UTAMA, CV</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>HAVANA TUNAS GEMILANG, PT</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7504</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jalan Karim Mahmud</t>
+          <t>JALAN DIPENOGORO BLOK PLAN PERKANTORAN MARISA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>52</v>
+        <v>1199</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NUANSA MANDIRI UTAMA, CV</t>
+          <t>SINAR GITA GEMILANG, CV</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>58.33333333333333</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
-      </c>
-      <c r="K43" t="n">
-        <v>90.90909090909091</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>96.44268774703556</v>
+        <v>47.04301075268817</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -2764,41 +2686,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ALDHIRA JAYA ABADI, CV</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>MEGA UTAMA MARISA, CV</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7504</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DUSUN BATU PASANG</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1083</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MULTI GADA PERKASA, CV</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>7503</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>JALAN THAYEB MOHAMAD GOBEL, DESA TINELO AYULA, KECAMATAN BULANGO SELATAN, KABUPATEN BONE BOLANGO, PROVINSI GORONTALO.</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1119</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ANTARIKSA JAYA, CV</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>60</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>78.57142857142857</v>
+      </c>
       <c r="L44" t="n">
-        <v>66.15384615384616</v>
+        <v>54.77574750830565</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2817,47 +2739,45 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SHINDY BAROKAH, CV</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
+          <t>ANNISA RAMADHANI PROPERTINDO, PT</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>7571</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dusun Mangrove</t>
+          <t>Jalan Profesor H.B Jassin Nomor 303</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>112</v>
+        <v>2035</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SHINDY BAROKAH, CV</t>
+          <t>POPA EYATO JAYA TAMA, PT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>92.30769230769231</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="L45" t="n">
-        <v>97.00854700854701</v>
+        <v>47.26885707419233</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -2872,41 +2792,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AMANAHMU, CV</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>NJ GROUP, CV</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>7571</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PERUM GRIYA MARISA INDAH, BLOK M, NOMOR 2</t>
+          <t>Perumahan Awara Karya Blok A.08</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1400</v>
+        <v>1790</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
+          <t>RIZKIA LESTARI, CV</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>75.86206896551724</v>
+      </c>
       <c r="L46" t="n">
-        <v>77.5</v>
+        <v>57.79028852920479</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2925,41 +2845,41 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CANANG SARI SEJAHTERA, CV</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>SULTAN JAYA NUSANTARA, CV</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kelurahan Kayumerah</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SULTAN JAYA NUSANTARA, CV</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>7502</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Desa Bongo III</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>694</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BINTANG FAJAR NUSANTARA, CV</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>65.38461538461539</v>
+        <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
-      </c>
-      <c r="K47" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>37.73584905660378</v>
+      </c>
       <c r="L47" t="n">
-        <v>70.15915119363396</v>
+        <v>64.33962264150944</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2978,41 +2898,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MITRA NUSANTARA INDONESIA, CV</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>INDRA PRAHASTA, CV</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7501</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JL. MARIDU HAYA NO.264A</t>
+          <t>Telaga Biru</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>458</v>
+        <v>1017</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MAWIRNA INDAH, CV</t>
+          <t>INDRA PRAHASTA, CV</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>60.86956521739131</v>
+        <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>27.77777777777778</v>
+      </c>
       <c r="L48" t="n">
-        <v>65.61264822134387</v>
+        <v>60.15873015873016</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3031,41 +2951,39 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LAKARA BUANA INDAH, CV</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>MOTIKACI FAMILY GROUP, CV</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7505</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dusun 2, Desa Pentadio Barat, Kab Gorontalo</t>
+          <t>Dusun Pasar Lama, Desa Moluo, Kecamatan Kwandang, Kabupaten Gorontalo Utara.</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MARKA INDAH, CV</t>
+          <t>GLAUKER FAMILY UTAMA, CV</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>70.27027027027026</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>74.84407484407484</v>
+        <v>49.37458854509546</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3084,45 +3002,43 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MANDIRI DUA, CV</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>MAHARANI PERSADA KONSTRUKSI, PT</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7504</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jl. Musa Kaluku</t>
+          <t>JALAN PROF. DR. ALOE SABOE</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>470</v>
+        <v>971</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DUTA MANDIRI, CV</t>
+          <t>MARLIMBO SEDAYA KONSTRUKSI, PT</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>90.32258064516128</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>92.35993208828522</v>
+        <v>57.68719539211342</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3137,41 +3053,41 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARTHA DENANTARA KONSTRUKSI, CV</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>RARA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Jalan Kancil</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>158</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>RARA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Jalan Dr. Umar Sidiki, Kel. Wonggaditi, Kec. Kota Utara, Kota Gorontalo, Provinsi Gorontalo</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1933</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>DAR AL TAUHID, CV</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>55.31914893617022</v>
+        <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>85.71428571428572</v>
+      </c>
       <c r="L51" t="n">
-        <v>60.57571964956196</v>
+        <v>76.62337662337661</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3190,41 +3106,41 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARMI PRATAMA JAYA, PT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>ALL AHAD, CV</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7502</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Desa Tanggilingo</t>
+          <t>Jalan husin DJ Rahman</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1188</v>
+        <v>58</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PURNAMA JAYA, CV</t>
+          <t>ALL AHAD, CV</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>64.86486486486487</v>
+        <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>92.30769230769231</v>
+      </c>
       <c r="L52" t="n">
-        <v>70.4864864864865</v>
+        <v>80.47337278106508</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3243,43 +3159,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SEXY ROAD INDO, CV</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>SANUR ARA, CV</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7571</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Perum Asabri Blok E/03</t>
+          <t>Jalan Gelatik No. 26</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2222</v>
+        <v>1177</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ALFA INDORAYA, CV</t>
+          <t>NUR ALAM, CV</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>57.14285714285714</v>
+        <v>80</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
-      </c>
-      <c r="K53" t="n">
-        <v>54.05405405405406</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>59.49455949455949</v>
+        <v>54.73684210526316</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3298,41 +3210,41 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SEXY ROAD INDO, CV</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>ABADI JAYA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>7502</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Desa Patoameme</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>433</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ABADI JAYA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Perum Asabri Blok E/03</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>MARKA INDAH, CV</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>60.60606060606061</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>41.66666666666666</v>
+      </c>
       <c r="L54" t="n">
-        <v>67.76859504132231</v>
+        <v>68.5185185185185</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3351,47 +3263,45 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMMA RAYA, CV</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>PUTRA ECHAXEL, CV</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Jalan Sultan Botutihe</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2132</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NURIAH INDAH, CV</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Jalan Rusli Datau 1 Perumahan Alya III Blok B Nomor 2</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>153</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>GAMMA RAYA, CV</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>100</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>92.92929292929293</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="L55" t="n">
-        <v>94.72186655285246</v>
+        <v>65.13032422123331</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3406,41 +3316,41 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TRI BAROKAH PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>VIJAYA KARYA UTAMA, PT</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>7571</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jl. Kasmat Lahay</t>
+          <t>Jl. Rusli Datau 2 No 4</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1191</v>
+        <v>2215</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PUTRA MITRA PERKASA, CV</t>
+          <t>MITRA JAYA MULTI SARANA, CV</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>65.21739130434783</v>
+        <v>44.89795918367348</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>92.6829268292683</v>
+      </c>
       <c r="L56" t="n">
-        <v>70.37037037037037</v>
+        <v>60.53558984569437</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3459,41 +3369,39 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INDO KONSTRUKSI PERSADA, PT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>AQIFFA JAYA MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7504</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Dusun Lamahu Desa Sipatana</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>486</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AAVAIRO MANDIRI JAYA, CV</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Jalan Sun Ismail Perum Latoro</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>207</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>LUTSIR PERSADA JAYA, PT</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>60</v>
+        <v>76.59574468085107</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>65.16129032258064</v>
+        <v>60.7483492296405</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3512,41 +3420,41 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HAVANA TUNAS GEMILANG, PT</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>NUSANTARA BOALEMO, CV</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7502</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JALAN DIPENOGORO BLOK PLAN PERKANTORAN MARISA</t>
+          <t>Dusun I</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1481</v>
+        <v>502</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>NUSANTARA BOALEMO, CV</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>56.00000000000001</v>
+        <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>43.47826086956522</v>
+      </c>
       <c r="L58" t="n">
-        <v>62.06896551724139</v>
+        <v>70.71611253196932</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3565,41 +3473,41 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEGA UTAMA MARISA, CV</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>MEGALODON CIPTA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DESA TOTO UTARA</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1512</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MEGALODON CIPTA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>7504</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>DUSUN BATU PASANG</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1426</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>MULIA MULTI MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>63.63636363636363</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>30.76923076923077</v>
+      </c>
       <c r="L59" t="n">
-        <v>69.45454545454545</v>
+        <v>67.87330316742081</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3618,43 +3526,41 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANNISA RAMADHANI PROPERTINDO, PT</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>RADESTA KONSTRUKSI, CV</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7501</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jalan Profesor H.B Jassin Nomor 303</t>
+          <t>Dusun IV</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2035</v>
+        <v>1025</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>POPA EYATO JAYA TAMA, PT</t>
+          <t>TRIJAYA MULTI KONSTRUKSI, CV</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>46.42857142857143</v>
+        <v>72</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>56.14035087719298</v>
+        <v>52.63157894736843</v>
       </c>
       <c r="L60" t="n">
-        <v>54.23417699177521</v>
+        <v>55.69590643274854</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3673,43 +3579,41 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ GROUP, CV</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>ALEXA STAR, CV</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7504</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Perumahan Awara Karya Blok A.08</t>
+          <t>Jl. Trans Sulawesi</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1790</v>
+        <v>415</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>RIZKIA LESTARI, CV</t>
+          <t>CENTRA MAKMUR, CV</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>40</v>
+        <v>58.06451612903225</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>75.86206896551724</v>
+        <v>97.14285714285714</v>
       </c>
       <c r="L61" t="n">
-        <v>68.76008804108584</v>
+        <v>67.40722774678632</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3728,41 +3632,39 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SULTAN JAYA NUSANTARA, CV</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>ARITO PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7502</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Dusun Gompase Induk</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>251</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ARYA PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Kelurahan Kayumerah</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>296</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>KARYA PATRIOT NUSANTARA, CV</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>73.07692307692308</v>
+        <v>84.84848484848484</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>76.79045092838197</v>
+        <v>62.71409749670619</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3781,41 +3683,39 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INDRA PRAHASTA, CV</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>ANSIR JAYA MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7505</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Desa Moluo</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>486</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AAVAIRO MANDIRI JAYA, CV</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Telaga Biru</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>292</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>INKA PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>76.47058823529412</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>80.74866310160428</v>
+        <v>64.90683229813665</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3834,41 +3734,41 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MOTIKACI FAMILY GROUP, CV</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
+          <t>FANTASTIC ENGINEER, CV</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>7501</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dusun Pasar Lama, Desa Moluo, Kecamatan Kwandang, Kabupaten Gorontalo Utara.</t>
+          <t>Dusun I Mekar Sari</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1597</v>
+        <v>9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TIRTA TARUNA, CV</t>
+          <t>FANTASTIC ENGINEER, CV</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>53.65853658536586</v>
+        <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>94.11764705882352</v>
+      </c>
       <c r="L64" t="n">
-        <v>60.05046257359125</v>
+        <v>84.65473145780051</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3887,41 +3787,39 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MAHARANI PERSADA KONSTRUKSI, PT</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>NAGITA CAHAYA MANDIRI, CV</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7503</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JALAN PROF. DR. ALOE SABOE</t>
+          <t>DESA TIMBUOLO</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1481</v>
+        <v>390</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RISKY MAHARANI ENERGI, PT</t>
+          <t>ZAHRAN CAHAYA MANDIRI, CV</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>60.71428571428572</v>
+        <v>84</v>
       </c>
       <c r="J65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>65.20408163265307</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3940,47 +3838,45 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>INDAH JAYA KARYA POHUWATO, PT</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7504</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jalan Kancil</t>
+          <t>jalan Pelabuhan</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>100</v>
+        <v>60.31746031746032</v>
       </c>
       <c r="J66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>85.71428571428572</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="L66" t="n">
-        <v>94.47004608294931</v>
+        <v>61.65079365079366</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -3995,47 +3891,45 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>DUA TUJUH SEDARAH, PT</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>7571</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jalan husin DJ Rahman</t>
+          <t>Jl. Kancil</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>58</v>
+        <v>2082</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
+          <t>TUJUH DUA JAYA, CV</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>92.30769230769231</v>
+        <v>50</v>
       </c>
       <c r="L67" t="n">
-        <v>95.63409563409563</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4050,43 +3944,39 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SANUR ARA, CV</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>PROSES GROUP, CV</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7571</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jalan Gelatik No. 26</t>
+          <t>Jalan Bandes, Kelurahan Bulotadaa Timur, Kecamatan Sipatana</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>146</v>
+        <v>1183</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SETIA KARYA SEJATI, CV</t>
+          <t>POHUWATO GROUP, CV</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>40</v>
+        <v>70.58823529411764</v>
       </c>
       <c r="J68" t="n">
-        <v>100</v>
-      </c>
-      <c r="K68" t="n">
-        <v>78.94736842105263</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>67.53911806543385</v>
+        <v>51.33689839572192</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4105,41 +3995,41 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PUTRA ECHAXEL, CV</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>7504</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jalan Sultan Botutihe</t>
+          <t>Jl. Pelabuhan</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1264</v>
+        <v>100</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>EKA PUTRA, CV</t>
+          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>73.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>100</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>96</v>
+      </c>
       <c r="L69" t="n">
-        <v>78.41269841269842</v>
+        <v>87.69811320754717</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4158,43 +4048,39 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VIJAYA KARYA UTAMA, PT</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>EKA PUTRA, CV</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>7504</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jl. Rusli Datau 2 No 4</t>
+          <t>Jalan Gagak, depan RM ASTA 6000, Desa Marisa Selatan, Kecamatan Marisa, Kabupaten Pohuwato</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2215</v>
+        <v>1264</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MITRA JAYA MULTI SARANA, CV</t>
+          <t>EKA PUTRA, CV</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>44.89795918367348</v>
+        <v>100</v>
       </c>
       <c r="J70" t="n">
-        <v>100</v>
-      </c>
-      <c r="K70" t="n">
-        <v>92.6829268292683</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>71.3912394225983</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4213,41 +4099,41 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AQIFFA JAYA MANDIRI, CV</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>TRI SANDI YUDHA, PT</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7571</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dusun Lamahu Desa Sipatana</t>
+          <t>Jalan Jakarta, Kompleks Perum Griya Wiyan Lestari Blok D Nomor 1</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1347</v>
+        <v>119</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JAYA MANDIRI PERSADA, CV</t>
+          <t>TRI SANDI YUDHA, PT</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>68.08510638297872</v>
+        <v>100</v>
       </c>
       <c r="J71" t="n">
-        <v>100</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>62.5</v>
+      </c>
       <c r="L71" t="n">
-        <v>72.81323877068559</v>
+        <v>66.29213483146067</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4266,47 +4152,43 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>ARUMI, CV</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>7501</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jl. Pelabuhan</t>
+          <t>JALAN SAMRATULANGI DUSUN I TENGAH, DESA YOSONEGORO, KECAMATAN LIMBOTO BARAT, KABUPATEN GORONTALO</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>972</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HARMONIS PERKASAINDAH POHUWATO, PT</t>
+          <t>ARUMI, CV</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>100</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
-      </c>
-      <c r="K72" t="n">
-        <v>96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>98.98039215686275</v>
+        <v>60</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4321,41 +4203,39 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EKA PUTRA, CV</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>TRISANDI LAGUNA, CV</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>7571</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jalan Gagak, depan RM ASTA 6000, Desa Marisa Selatan, Kecamatan Marisa, Kabupaten Pohuwato</t>
+          <t>Jalan Bali Perum Hafair Mas Blok B</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1419</v>
+        <v>1597</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LOMAYA PUTRA, CV</t>
+          <t>TIRTA TARUNA, CV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>75.86206896551724</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="J73" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>81.54158215010142</v>
+        <v>52.11428571428571</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4374,43 +4254,41 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TRI SANDI YUDHA, PT</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>DHARMA BAKTI, CV</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>7501</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jalan Jakarta, Kompleks Perum Griya Wiyan Lestari Blok D Nomor 1</t>
+          <t>JL. RAYA LIMBOTO NO. 9</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>119</v>
+        <v>928</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TRI SANDI YUDHA, PT</t>
+          <t>DHARMA BAKTI, CV</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>100</v>
       </c>
       <c r="J74" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>62.5</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="L74" t="n">
-        <v>72.41379310344827</v>
+        <v>83.98268398268398</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4429,41 +4307,41 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARUMI, CV</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>GOMINA PERMAI INDAH, CV</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>7503</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JALAN SAMRATULANGI DUSUN I TENGAH, DESA YOSONEGORO, KECAMATAN LIMBOTO BARAT, KABUPATEN GORONTALO</t>
+          <t>Jalan Nani Wartabone</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ARSA, CV</t>
+          <t>GOMINA PERMAI INDAH, CV</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>70.58823529411764</v>
+        <v>100</v>
       </c>
       <c r="J75" t="n">
-        <v>100</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>37.5</v>
+      </c>
       <c r="L75" t="n">
-        <v>79.63800904977376</v>
+        <v>62.24489795918367</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4482,45 +4360,43 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DHARMA BAKTI, CV</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
+          <t>ALIF SATYA PERKASA, PT</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>JL. RAYA LIMBOTO NO. 9</t>
+          <t>DESA TINELO</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>421</v>
+        <v>509</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>RAHMAT ABADI, CV</t>
+          <t>ALIF SETYA PERKASA, PT</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>68.75</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="J76" t="n">
-        <v>100</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>100</v>
+      </c>
       <c r="L76" t="n">
-        <v>75</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -4535,41 +4411,41 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GOMINA PERMAI INDAH, CV</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>MADINA MULTI KREASI, CV</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>7501</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jalan Nani Wartabone</t>
+          <t>JALAN JARWADI LINGKUNGAN I</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1151</v>
+        <v>737</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GLORIA INDAH, CV</t>
+          <t>MADINA MULTI KREASI, CV</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>71.7948717948718</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>100</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>47.88732394366198</v>
+      </c>
       <c r="L77" t="n">
-        <v>75.97340930674264</v>
+        <v>64.45582586427656</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -4588,43 +4464,45 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ALIF SATYA PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>SELTA LESTARI, CV</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>7504</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DESA TINELO</t>
+          <t>Dusun Teratai</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>509</v>
+        <v>1195</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ALIF SETYA PERKASA, PT</t>
+          <t>SELTA LESTARI, CV</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>95.45454545454545</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>100</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="L78" t="n">
-        <v>96.96969696969697</v>
+        <v>80.32407407407408</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4639,43 +4517,45 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ALIF SATYA PERKASA, PT</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>GARUDA SAKTI, CV</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>7571</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DESA TINELO</t>
+          <t>JALAN MATOLODULA</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>509</v>
+        <v>2047</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ALIF SETYA PERKASA, PT</t>
+          <t>GARUDA SAKTI, CV</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>95.45454545454545</v>
+        <v>100</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>100</v>
+        <v>89.65517241379311</v>
       </c>
       <c r="L79" t="n">
-        <v>96.96969696969697</v>
+        <v>79.85480943738658</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4690,41 +4570,39 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MADINA MULTI KREASI, CV</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>TULUS RAJAWALI GORONTALO, PT</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>7503</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JALAN JARWADI LINGKUNGAN I</t>
+          <t>DESA TOTO SELATAN</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>444</v>
+        <v>1440</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SEMANGAT KARYA, CV</t>
+          <t>TULUS RAJAWALI GORONTALO, PT</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>63.41463414634146</v>
+        <v>100</v>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
-        <v>68.83468834688347</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4743,41 +4621,41 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SELTA LESTARI, CV</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>SINAR BATU ALAM, CV</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>7501</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dusun Teratai</t>
+          <t>Jl. JENDRAL SUDIRMAN</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1434</v>
+        <v>911</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SINAR LESTARI, CV</t>
+          <t>SINAR BATU ALAM, CV</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>82.35294117647058</v>
+        <v>100</v>
       </c>
       <c r="J81" t="n">
-        <v>100</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>74.41860465116279</v>
+      </c>
       <c r="L81" t="n">
-        <v>85.71428571428571</v>
+        <v>75.29715762273902</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4796,47 +4674,45 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GARUDA SAKTI, CV</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>PUTRA DEZA, CV</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>7501</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>JALAN MATOLODULA</t>
+          <t>DUSUN MUARA</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2047</v>
+        <v>34</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>GARUDA SAKTI, CV</t>
+          <t>PUTRA DEZA, CV</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I82" t="n">
         <v>100</v>
       </c>
       <c r="J82" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>89.65517241379311</v>
+        <v>90</v>
       </c>
       <c r="L82" t="n">
-        <v>95.40229885057471</v>
+        <v>77.09677419354838</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -4851,41 +4727,39 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TULUS RAJAWALI GORONTALO, PT</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>ABADI JAYA BERSAMA NEW, CV</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>7504</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DESA TOTO SELATAN</t>
+          <t>DESA BUNUYO KECAMATAN PAGUAT</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1136</v>
+        <v>709</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>KURNIA LOGISTIK PRATAMA, PT</t>
+          <t>TILANGO JAYA BERSAMA, CV</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>47.27272727272728</v>
+        <v>68</v>
       </c>
       <c r="J83" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
-        <v>53.86363636363637</v>
+        <v>55.25</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -4904,41 +4778,39 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SINAR BATU ALAM, CV</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>ARMADAN JAYA, CV</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>7501</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jl. JENDRAL SUDIRMAN</t>
+          <t>Jalan Hasan Dangkua Lingkungan I</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>246</v>
+        <v>41</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SINAR ALINKO, CV</t>
+          <t>ARMADAN JAYA, CV</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>68.57142857142857</v>
+        <v>100</v>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
-        <v>74.03726708074534</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -4957,47 +4829,43 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PUTRA DEZA, CV</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SURYA SINTESIA, CV</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>7571</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DUSUN MUARA</t>
+          <t>JALAN PADANG PERUMAHAN GRAHA 42 BLOK E NO.3</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>34</v>
+        <v>885</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PUTRA DEZA, CV</t>
+          <t>SURYA LINTAS, CV</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>100</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="J85" t="n">
-        <v>100</v>
-      </c>
-      <c r="K85" t="n">
-        <v>90</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>96.20689655172414</v>
+        <v>61.76470588235293</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5012,41 +4880,41 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ABADI JAYA BERSAMA NEW, CV</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>SENCIKA INDAH, CV</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>7504</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DESA BUNUYO KECAMATAN PAGUAT</t>
+          <t>Jln. Pelabuhan Marisa</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1392</v>
+        <v>1156</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CITRA ABDI KARYA, CV</t>
+          <t>INDAH JAYA, CV</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>65.21739130434783</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="J86" t="n">
-        <v>100</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>72.72727272727273</v>
+      </c>
       <c r="L86" t="n">
-        <v>69.85507246376811</v>
+        <v>59.63743001866169</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -5065,41 +4933,41 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ARMADAN JAYA, CV</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>7571</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jalan Hasan Dangkua Lingkungan I</t>
+          <t>JALAN CUT NYAK DIEN</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>275</v>
+        <v>2194</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CAHAYA AGRO KARYA, CV</t>
+          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>64.86486486486487</v>
+        <v>100</v>
       </c>
       <c r="J87" t="n">
-        <v>100</v>
-      </c>
-      <c r="K87" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>91.42857142857143</v>
+      </c>
       <c r="L87" t="n">
-        <v>71.8918918918919</v>
+        <v>85.32967032967032</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -5118,43 +4986,41 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SURYA SINTESIA, CV</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>SINAR PUTRI PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>7501</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>JALAN PADANG PERUMAHAN GRAHA 42 BLOK E NO.3</t>
+          <t>Jalan PGRI</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2214</v>
+        <v>652</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SURYA SINTESIA, CV</t>
+          <t>SINAR PUTRI PRATAMA, CV</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I88" t="n">
         <v>100</v>
       </c>
       <c r="J88" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>50.84745762711864</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="L88" t="n">
-        <v>67.48370273794004</v>
+        <v>66.30036630036631</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -5173,41 +5039,41 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SENCIKA INDAH, CV</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>BAYOORS, CV</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Jl. -</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1460</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>BAYOORS, CV</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>7504</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Jln. Pelabuhan Marisa</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1442</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>NUSA INDAH, CV</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>77.41935483870968</v>
+        <v>100</v>
       </c>
       <c r="J89" t="n">
-        <v>100</v>
-      </c>
-      <c r="K89" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>20</v>
+      </c>
       <c r="L89" t="n">
-        <v>81.72043010752688</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -5226,47 +5092,45 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>KARYA JAYA BERSAMA, CV</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>7501</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>JALAN CUT NYAK DIEN</t>
+          <t>Dusun Motolohu</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2194</v>
+        <v>655</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ANDARA ARTHA KONSTRUKSI, PT</t>
+          <t>KARYA JAYA BERSAMA, CV</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I90" t="n">
         <v>100</v>
       </c>
       <c r="J90" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>91.42857142857143</v>
+        <v>32</v>
       </c>
       <c r="L90" t="n">
-        <v>96.74285714285713</v>
+        <v>63.04761904761905</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5281,41 +5145,41 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SINAR PUTRI PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>ALYA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>7571</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jalan PGRI</t>
+          <t>Jalan Kancil</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>375</v>
+        <v>158</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SINAR PURNAMA, CV</t>
+          <t>RARA BERKAH, CV</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J91" t="n">
-        <v>100</v>
-      </c>
-      <c r="K91" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>85.71428571428572</v>
+      </c>
       <c r="L91" t="n">
-        <v>78.70370370370371</v>
+        <v>61.47186147186148</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -5334,41 +5198,41 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BAYOORS, CV</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>INDAH RAHAYU, CV</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>7501</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jl. -</t>
+          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1139</v>
+        <v>790</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CITOS, CV</t>
+          <t>INDAH RAHAYU, CV</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J92" t="n">
-        <v>100</v>
-      </c>
-      <c r="K92" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>51.16279069767442</v>
+      </c>
       <c r="L92" t="n">
-        <v>70.66666666666667</v>
+        <v>59.9483204134367</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -5387,43 +5251,41 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KARYA JAYA BERSAMA, CV</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>NURUL YAKIN, CV</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7504</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dusun Motolohu</t>
+          <t>Jln. Sultan Amai</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>227</v>
+        <v>1253</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>KARYA BERSAMA, CV</t>
+          <t>NURUL YAKIN, CV</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>87.17948717948718</v>
+        <v>100</v>
       </c>
       <c r="J93" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>27.45098039215686</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="L93" t="n">
-        <v>67.55656108597285</v>
+        <v>80.90090090090089</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -5442,41 +5304,41 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INDAH RAHAYU, CV</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>WAHYU, CV</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>7503</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
+          <t>Jl. Kesehatan, Desa Toto Utara</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>291</v>
+        <v>1360</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INDAH KERAMIK, CV</t>
+          <t>WAHYU, CV</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>72.72727272727273</v>
+        <v>100</v>
       </c>
       <c r="J94" t="n">
-        <v>100</v>
-      </c>
-      <c r="K94" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>62.5</v>
+      </c>
       <c r="L94" t="n">
-        <v>78.18181818181819</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -5495,41 +5357,41 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NURUL YAKIN, CV</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>SUNGAI BONE GORONTALO, CV</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>7571</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jln. Sultan Amai</t>
+          <t>JALAN PALMA</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1431</v>
+        <v>2098</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>RIDWAN, CV</t>
+          <t>SUNGAI BONE GORONTALO, CV</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>56.00000000000001</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>100</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>44.99999999999999</v>
+      </c>
       <c r="L95" t="n">
-        <v>65.26315789473684</v>
+        <v>71.30952380952381</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -5548,41 +5410,39 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WAHYU, CV</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>CAHAYA BULAN, CV</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7501</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jl. Kesehatan, Desa Toto Utara</t>
+          <t>Dusun Lamahu</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1160</v>
+        <v>592</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>JDS RAYA, CV</t>
+          <t>CAHAYA BINTANG, CV</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>57.14285714285714</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="J96" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>70.32967032967032</v>
+        <v>59.89304812834224</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -5601,47 +5461,45 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>ALLIESSAN, PT</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>JL. SULTAN HASANUDDIN</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ALLIESSAN, PT</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>JALAN PALMA</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>2098</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I97" t="n">
         <v>100</v>
       </c>
       <c r="J97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>44.99999999999999</v>
+        <v>95</v>
       </c>
       <c r="L97" t="n">
-        <v>84.875</v>
+        <v>82.375</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5656,41 +5514,41 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAHAYA BULAN, CV</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>7571</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dusun Lamahu</t>
+          <t>Jalan Beringin</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>414</v>
+        <v>1683</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CAHAYA AGUNG, CV</t>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
-      </c>
-      <c r="K98" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>50.90909090909091</v>
+      </c>
       <c r="L98" t="n">
-        <v>85</v>
+        <v>70.74380165289257</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -5709,47 +5567,45 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ALLIESSAN, PT</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>ZIITEK, CV</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>7503</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JL. SULTAN HASANUDDIN</t>
+          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2240</v>
+        <v>892</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ALLIESSAN, PT</t>
+          <t>UTAMA KARYA, CV</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J99" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>95</v>
+        <v>49.57264957264957</v>
       </c>
       <c r="L99" t="n">
-        <v>97.23684210526316</v>
+        <v>44.59591041869523</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5764,47 +5620,43 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>USAHA SEJAHTERA, CV</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>7504</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jalan Beringin</t>
+          <t>Jl. Pelabuhan</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1683</v>
+        <v>1217</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
+          <t>USAHA SEJAHTERA, CV</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I100" t="n">
         <v>100</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
-      </c>
-      <c r="K100" t="n">
-        <v>50.90909090909091</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>83.63636363636364</v>
+        <v>76</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -5819,41 +5671,41 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZIITEK, CV</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>TRIANA, CV</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>7501</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
+          <t>Perum Azizah Permai Blok I Nomor 3</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1208</v>
+        <v>668</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SPEKTEK, CV</t>
+          <t>UNGKAI KARYA, CV</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>66.66666666666667</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="J101" t="n">
-        <v>100</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>75.75757575757575</v>
+      </c>
       <c r="L101" t="n">
-        <v>76.19047619047619</v>
+        <v>62.28438228438228</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -5872,41 +5724,41 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USAHA SEJAHTERA, CV</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>BINTANG ADZKIA, CV</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>7501</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jl. Pelabuhan</t>
+          <t>Jalan A. Otoluwa</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1404</v>
+        <v>572</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BRESCIA SEJAHTERA SELATAN, PT</t>
+          <t>BINTANG ADZKIA, CV</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J102" t="n">
-        <v>100</v>
-      </c>
-      <c r="K102" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>85.71428571428572</v>
+      </c>
       <c r="L102" t="n">
-        <v>69.02173913043478</v>
+        <v>79.28571428571429</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -5925,41 +5777,39 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TRIANA, CV</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>ZAHRA GEMILANG, CV</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>7501</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Perum Azizah Permai Blok I Nomor 3</t>
+          <t>DUSUN II</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>364</v>
+        <v>593</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
+          <t>GEMILANG, CV</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>78.26086956521739</v>
+        <v>80</v>
       </c>
       <c r="J103" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>84.47204968944099</v>
+        <v>60</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -5970,49 +5820,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sijk</t>
+          <t>lpse</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BINTANG ADZKIA, CV</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>HADFIR PERKASA, CV</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>7502</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jalan A. Otoluwa</t>
+          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>263</v>
+        <v>844</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ANUGERAH ABADI, CV</t>
+          <t>DWI AULIA PERKASA, CV</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>61.11111111111111</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="J104" t="n">
         <v>100</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
-        <v>68.18181818181819</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -6027,45 +5875,43 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HADFIR PERKASA, CV</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>TULUS MULIA, CV</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>7571</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
+          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>844</v>
+        <v>1906</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DWI AULIA PERKASA, CV</t>
+          <t>LIMA SATU, CV</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>71.7948717948718</v>
+        <v>64.28571428571428</v>
       </c>
       <c r="J105" t="n">
         <v>100</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
-        <v>76.92307692307692</v>
+        <v>71.80451127819549</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6080,45 +5926,43 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TULUS MULIA, CV</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>DWI SAMA, CV</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>7504</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
+          <t>DESA TALANGO KECAMATAN KABILA</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1906</v>
+        <v>1408</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LIMA SATU, CV</t>
+          <t>DIRAHMATI, CV</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.28571428571428</v>
+        <v>72</v>
       </c>
       <c r="J106" t="n">
         <v>100</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
-        <v>71.80451127819549</v>
+        <v>79</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -6133,45 +5977,45 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DWI SAMA, CV</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>AZRAM MAJU BERSAMA, CV</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>7571</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DESA TALANGO KECAMATAN KABILA</t>
+          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1408</v>
+        <v>145</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIRAHMATI, CV</t>
+          <t>AZRAM MAJU BERSAMA, CV</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
         <v>100</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>42.30769230769231</v>
+      </c>
       <c r="L107" t="n">
-        <v>79</v>
+        <v>66.89785624211854</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -6186,34 +6030,32 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AZRAM MAJU BERSAMA, CV</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>AMIN, CV</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>7504</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
+          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>145</v>
+        <v>1400</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>AZRAM MAJU BERSAMA, CV</t>
+          <t>AMIN, CV</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6222,15 +6064,13 @@
       <c r="J108" t="n">
         <v>100</v>
       </c>
-      <c r="K108" t="n">
-        <v>42.30769230769231</v>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
-        <v>66.89785624211854</v>
+        <v>100</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6241,49 +6081,49 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>BINTANG PALMA, CV</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>7571</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
+          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1400</v>
+        <v>1955</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>AMIN, CV</t>
+          <t>ADI CIPTA UTAMAI, CV</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>100</v>
+        <v>59.45945945945945</v>
       </c>
       <c r="J109" t="n">
         <v>100</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>55.67010309278351</v>
+      </c>
       <c r="L109" t="n">
-        <v>100</v>
+        <v>59.12351231938861</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -6294,21 +6134,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BINTANG PALMA, CV</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>MITRA CAHAYA TANAMON, CV</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7571</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
+          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6325,16 +6163,16 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>59.45945945945945</v>
+        <v>50</v>
       </c>
       <c r="J110" t="n">
         <v>100</v>
       </c>
       <c r="K110" t="n">
-        <v>55.67010309278351</v>
+        <v>68.08510638297872</v>
       </c>
       <c r="L110" t="n">
-        <v>59.12351231938861</v>
+        <v>63.94479585968948</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -6349,47 +6187,43 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MITRA CAHAYA TANAMON, CV</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>RIZKY ADITYA PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7504</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
+          <t>Desa Tanah Putih Kecamatan Botupingge</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1955</v>
+        <v>1492</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ADI CIPTA UTAMAI, CV</t>
+          <t>TITIAN PRATAMA, CV</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>50</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="J111" t="n">
         <v>100</v>
       </c>
-      <c r="K111" t="n">
-        <v>68.08510638297872</v>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
-        <v>63.94479585968948</v>
+        <v>67.34693877551021</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -6404,45 +6238,43 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RIZKY ADITYA PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
+          <t>ARITO PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>7501</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Desa Tanah Putih Kecamatan Botupingge</t>
+          <t>JL. TRANS SULAWESI DESA MOLOMBULAHE KECAMATAN PAGUYAMAN</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1492</v>
+        <v>251</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>TITIAN PRATAMA, CV</t>
+          <t>ARYA PRATAMA, CV</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>61.90476190476191</v>
+        <v>84.84848484848484</v>
       </c>
       <c r="J112" t="n">
         <v>100</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
-        <v>67.34693877551021</v>
+        <v>87.73448773448773</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -6457,45 +6289,43 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ARITO PRATAMA, CV</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>ANUGERAH BERSAMA, CV</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>7502</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>JL. TRANS SULAWESI DESA MOLOMBULAHE KECAMATAN PAGUYAMAN</t>
+          <t>Jln Basoe Bobihoe</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>251</v>
+        <v>828</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ARYA PRATAMA, CV</t>
+          <t>BERKAH ANUGRAH, CV</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>84.84848484848484</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="J113" t="n">
         <v>100</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>87.73448773448773</v>
+        <v>82.45614035087719</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -6510,49 +6340,49 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ANUGERAH BERSAMA, CV</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>ARVID, CV</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7571</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jln Basoe Bobihoe</t>
+          <t>Jln. Jambura</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>828</v>
+        <v>157</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BERKAH ANUGRAH, CV</t>
+          <t>ARVID, CV</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>78.94736842105263</v>
+        <v>100</v>
       </c>
       <c r="J114" t="n">
         <v>100</v>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>90.90909090909091</v>
+      </c>
       <c r="L114" t="n">
-        <v>82.45614035087719</v>
+        <v>95.63636363636364</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6563,34 +6393,32 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ARVID, CV</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>PRIMADONA, CV</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7501</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Jln. Jambura</t>
+          <t>Desa Limbato Kec. Tilamuta</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>157</v>
+        <v>364</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ARVID, CV</t>
+          <t>PRIMADONA, CV</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6599,11 +6427,9 @@
       <c r="J115" t="n">
         <v>100</v>
       </c>
-      <c r="K115" t="n">
-        <v>90.90909090909091</v>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>95.63636363636364</v>
+        <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -6618,49 +6444,47 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PRIMADONA, CV</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>ALL AHAD, CV</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>267</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>BAROKAH ABADI, CV</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Desa Limbato Kec. Tilamuta</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>364</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>PRIMADONA, CV</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>100</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="J116" t="n">
         <v>100</v>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
-        <v>100</v>
+        <v>71.55172413793103</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>INSERT</t>
         </is>
       </c>
     </row>
@@ -6671,45 +6495,45 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ALL AHAD, CV</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
+          <t>SATYA HARDANA, CV</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>7571</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
+          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>267</v>
+        <v>138</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>BAROKAH ABADI, CV</t>
+          <t>SATYA HARDANA, CV</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>62.06896551724138</v>
+        <v>100</v>
       </c>
       <c r="J117" t="n">
         <v>100</v>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>53.84615384615385</v>
+      </c>
       <c r="L117" t="n">
-        <v>71.55172413793103</v>
+        <v>71.15384615384616</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -6724,47 +6548,43 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SATYA HARDANA, CV</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+          <t>RARA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7571</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1933</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DAR AL TAUHID, CV</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>138</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>SATYA HARDANA, CV</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
         <v>100</v>
       </c>
-      <c r="K118" t="n">
-        <v>53.84615384615385</v>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>71.15384615384616</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -6779,45 +6599,43 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
+          <t>FELQIMUN ADIJAYA, CV</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>7502</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
+          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1933</v>
+        <v>758</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DAR AL TAUHID, CV</t>
+          <t>ADHITYA, CV</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>58.06451612903225</v>
       </c>
       <c r="J119" t="n">
         <v>100</v>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>60.52631578947368</v>
+        <v>65.05376344086021</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -6832,49 +6650,47 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FELQIMUN ADIJAYA, CV</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
+          <t>ANTARIKSA PERSADA, CV</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>7503</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
+          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>758</v>
+        <v>1226</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ADHITYA, CV</t>
+          <t>ANTARIKSA PERSADA, CV</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>58.06451612903225</v>
+        <v>100</v>
       </c>
       <c r="J120" t="n">
         <v>100</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>65.05376344086021</v>
+        <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DROP</t>
         </is>
       </c>
     </row>
@@ -6885,34 +6701,32 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ANTARIKSA PERSADA, CV</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
+          <t>SEXY ROAD INDO, CV</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>7502</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
+          <t>Perum Asabri Blok E no 3, Ulapato A</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1226</v>
+        <v>55</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ANTARIKSA PERSADA, CV</t>
+          <t>SEXY ROAD INDO, CV</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6921,66 +6735,13 @@
       <c r="J121" t="n">
         <v>100</v>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>77.41935483870968</v>
+      </c>
       <c r="L121" t="n">
-        <v>100</v>
+        <v>86.13469156762875</v>
       </c>
       <c r="M121" t="inlineStr">
-        <is>
-          <t>DROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>lpse</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>17</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>SEXY ROAD INDO, CV</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Perum Asabri Blok E no 3, Ulapato A</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>55</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>SEXY ROAD INDO, CV</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>100</v>
-      </c>
-      <c r="J122" t="n">
-        <v>100</v>
-      </c>
-      <c r="K122" t="n">
-        <v>77.41935483870968</v>
-      </c>
-      <c r="L122" t="n">
-        <v>86.13469156762875</v>
-      </c>
-      <c r="M122" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
